--- a/reports/test-cases-filled.xlsx
+++ b/reports/test-cases-filled.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="590">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -249,6 +249,9 @@
     <t>Access is granted to all instance level functions</t>
   </si>
   <si>
+    <t>Automated check failed: Error: Sidebar entry "Users" should be available</t>
+  </si>
+  <si>
     <t xml:space="preserve">USER MANAGEMENT </t>
   </si>
   <si>
@@ -266,6 +269,9 @@
   </si>
   <si>
     <t>- List of users displayed.- Users show key attributes (name, email, role, country, status, association).</t>
+  </si>
+  <si>
+    <t>Automated check failed: Test timeout of 30000ms exceeded while running "beforeEach" hook.</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC02</t>
@@ -302,9 +308,6 @@
     <t>- Only users from selected country are displayed.</t>
   </si>
   <si>
-    <t>Automated check failed: Error: No location/country filter control is present on the Users list</t>
-  </si>
-  <si>
     <t>IA-FM01-F15-TC04</t>
   </si>
   <si>
@@ -321,9 +324,6 @@
     <t>- Users displayed match selected role.</t>
   </si>
   <si>
-    <t>Automated check failed: Error: No role filter control is present on the Users list</t>
-  </si>
-  <si>
     <t>IA-FM01-F15-TC05</t>
   </si>
   <si>
@@ -337,9 +337,6 @@
   </si>
   <si>
     <t>- Only users with selected status are shown.</t>
-  </si>
-  <si>
-    <t>Automated check failed: Error: No status filter control is present on the Users list</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC06</t>
@@ -572,9 +569,6 @@
   </si>
   <si>
     <t>Permission assigned</t>
-  </si>
-  <si>
-    <t>Automated check failed: Error: No permission-assignment UI is present in the role editor (only an Active toggle exists)</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC09</t>
@@ -750,6 +744,9 @@
     <t xml:space="preserve"> level created successfully</t>
   </si>
   <si>
+    <t>Automated check failed: Error: expect(locator).toBeVisible() failed</t>
+  </si>
+  <si>
     <t>IA-FM01-F10-TC02</t>
   </si>
   <si>
@@ -854,9 +851,6 @@
     <t>Inactive not visible</t>
   </si>
   <si>
-    <t>Automated check failed: Error: Inactive level should not be visible in the default list</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC09</t>
   </si>
   <si>
@@ -907,9 +901,6 @@
     <t>Location level not listed on options</t>
   </si>
   <si>
-    <t>Automated check failed: Error: Location form uses a free-text Level ID (no options list), so inactive-level exclusion cannot be enforced/verified here</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC12</t>
   </si>
   <si>
@@ -999,9 +990,6 @@
     <t>All users exported</t>
   </si>
   <si>
-    <t>Automated check failed: Error: No export/download control is present on the Users list</t>
-  </si>
-  <si>
     <t>IA-FM01-F15-TC15</t>
   </si>
   <si>
@@ -1247,9 +1235,6 @@
   </si>
   <si>
     <t>- Only associations from selected country displayed.</t>
-  </si>
-  <si>
-    <t>Automated check failed: Error: No country/location filter control on the Associations list (only status tabs exist)</t>
   </si>
   <si>
     <t>IA-CM05-F01-TC04</t>
@@ -1716,9 +1701,6 @@
   </si>
   <si>
     <t>List of email templates displays</t>
-  </si>
-  <si>
-    <t>Automated check failed: Error: No Email/SMS template configuration section is exposed in the instance admin portal navigation</t>
   </si>
   <si>
     <t xml:space="preserve"> IA-FM01-F22-TC02</t>
@@ -2468,10 +2450,10 @@
         <v>45935</v>
       </c>
       <c r="O3" s="18">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P3" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -2516,10 +2498,10 @@
         <v>45935</v>
       </c>
       <c r="O4" s="18">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P4" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2700,10 +2682,10 @@
       <c r="M8" s="5"/>
       <c r="N8" s="12"/>
       <c r="O8" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P8" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2774,10 +2756,10 @@
         <v>45935</v>
       </c>
       <c r="O10" s="18">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P10" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2822,10 +2804,10 @@
         <v>45935</v>
       </c>
       <c r="O11" s="18">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P11" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2848,13 +2830,13 @@
         <v>35</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="J12" s="17">
         <v>45877</v>
@@ -2870,15 +2852,15 @@
         <v>45935</v>
       </c>
       <c r="O12" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P12" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2900,31 +2882,31 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J14" s="17">
         <v>45877</v>
@@ -2940,39 +2922,39 @@
         <v>45935</v>
       </c>
       <c r="O14" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P14" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="J15" s="17">
         <v>45877</v>
@@ -2988,27 +2970,27 @@
         <v>45935</v>
       </c>
       <c r="O15" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P15" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>35</v>
@@ -3020,7 +3002,7 @@
         <v>23</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J16" s="17">
         <v>45877</v>
@@ -3036,27 +3018,27 @@
         <v>45935</v>
       </c>
       <c r="O16" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P16" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>35</v>
@@ -3068,7 +3050,7 @@
         <v>23</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J17" s="17">
         <v>45877</v>
@@ -3084,10 +3066,10 @@
         <v>45935</v>
       </c>
       <c r="O17" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P17" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -3116,7 +3098,7 @@
         <v>23</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="J18" s="17">
         <v>45877</v>
@@ -3132,39 +3114,39 @@
         <v>45935</v>
       </c>
       <c r="O18" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P18" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="D19" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>106</v>
-      </c>
       <c r="F19" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J19" s="17">
         <v>45877</v>
@@ -3180,27 +3162,27 @@
         <v>45935</v>
       </c>
       <c r="O19" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P19" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>109</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>110</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>35</v>
@@ -3212,7 +3194,7 @@
         <v>23</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J20" s="17">
         <v>45877</v>
@@ -3232,31 +3214,31 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="C21" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="E21" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>115</v>
-      </c>
       <c r="F21" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J21" s="17">
         <v>45877</v>
@@ -3272,27 +3254,27 @@
         <v>45935</v>
       </c>
       <c r="O21" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P21" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="C22" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="15" t="s">
         <v>118</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>119</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>35</v>
@@ -3304,7 +3286,7 @@
         <v>23</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J22" s="17">
         <v>45877</v>
@@ -3324,19 +3306,19 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="E23" s="15" t="s">
         <v>123</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>124</v>
       </c>
       <c r="F23" s="16" t="s">
         <v>35</v>
@@ -3348,7 +3330,7 @@
         <v>23</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J23" s="17">
         <v>45877</v>
@@ -3368,19 +3350,19 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>128</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>129</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>35</v>
@@ -3392,7 +3374,7 @@
         <v>23</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J24" s="17">
         <v>45877</v>
@@ -3412,19 +3394,19 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>134</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>35</v>
@@ -3436,7 +3418,7 @@
         <v>23</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J25" s="17">
         <v>45877</v>
@@ -3456,7 +3438,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -3476,31 +3458,31 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C27" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="F27" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J27" s="17">
         <v>45877</v>
@@ -3516,39 +3498,39 @@
         <v>45935</v>
       </c>
       <c r="O27" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P27" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="F28" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J28" s="17">
         <v>45877</v>
@@ -3564,39 +3546,39 @@
         <v>45935</v>
       </c>
       <c r="O28" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P28" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="C29" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>149</v>
-      </c>
       <c r="F29" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J29" s="17">
         <v>45877</v>
@@ -3612,39 +3594,39 @@
         <v>45935</v>
       </c>
       <c r="O29" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P29" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="C30" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="F30" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J30" s="17">
         <v>45877</v>
@@ -3660,39 +3642,39 @@
         <v>45935</v>
       </c>
       <c r="O30" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P30" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="C31" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="E31" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>158</v>
-      </c>
       <c r="F31" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J31" s="17">
         <v>45877</v>
@@ -3708,39 +3690,39 @@
         <v>45935</v>
       </c>
       <c r="O31" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P31" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="C32" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D32" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="E32" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="F32" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J32" s="17">
         <v>45877</v>
@@ -3756,39 +3738,39 @@
         <v>45935</v>
       </c>
       <c r="O32" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P32" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="D33" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="E33" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>168</v>
-      </c>
       <c r="F33" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J33" s="17">
         <v>45877</v>
@@ -3804,27 +3786,27 @@
         <v>45935</v>
       </c>
       <c r="O33" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P33" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C34" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>172</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>35</v>
@@ -3836,7 +3818,7 @@
         <v>23</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="J34" s="17">
         <v>45877</v>
@@ -3852,27 +3834,27 @@
         <v>45935</v>
       </c>
       <c r="O34" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P34" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="E35" s="15" t="s">
         <v>175</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>177</v>
       </c>
       <c r="F35" s="16" t="s">
         <v>35</v>
@@ -3884,7 +3866,7 @@
         <v>23</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="J35" s="17">
         <v>45877</v>
@@ -3900,27 +3882,27 @@
         <v>45935</v>
       </c>
       <c r="O35" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P35" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="D36" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="E36" s="15" t="s">
         <v>180</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>182</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>35</v>
@@ -3932,7 +3914,7 @@
         <v>23</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="J36" s="17">
         <v>45877</v>
@@ -3948,27 +3930,27 @@
         <v>45935</v>
       </c>
       <c r="O36" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P36" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="D37" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="E37" s="15" t="s">
         <v>185</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>187</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>35</v>
@@ -3980,7 +3962,7 @@
         <v>23</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="J37" s="17">
         <v>45877</v>
@@ -3996,27 +3978,27 @@
         <v>45935</v>
       </c>
       <c r="O37" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P37" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="D38" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="E38" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>192</v>
       </c>
       <c r="F38" s="16" t="s">
         <v>35</v>
@@ -4028,7 +4010,7 @@
         <v>23</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J38" s="17">
         <v>45877</v>
@@ -4048,19 +4030,19 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="E39" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>197</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>35</v>
@@ -4072,7 +4054,7 @@
         <v>23</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J39" s="17">
         <v>45877</v>
@@ -4092,19 +4074,19 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="D40" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="E40" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="F40" s="16" t="s">
         <v>35</v>
@@ -4116,7 +4098,7 @@
         <v>23</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J40" s="17">
         <v>45877</v>
@@ -4136,19 +4118,19 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="E41" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>206</v>
       </c>
       <c r="F41" s="16" t="s">
         <v>35</v>
@@ -4160,7 +4142,7 @@
         <v>23</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J41" s="17">
         <v>45877</v>
@@ -4180,19 +4162,19 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="D42" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="E42" s="15" t="s">
         <v>209</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>211</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>35</v>
@@ -4224,19 +4206,19 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="D43" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="E43" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>216</v>
       </c>
       <c r="F43" s="16" t="s">
         <v>35</v>
@@ -4268,19 +4250,19 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="E44" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>220</v>
       </c>
       <c r="F44" s="16" t="s">
         <v>35</v>
@@ -4312,19 +4294,19 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="E45" s="15" t="s">
         <v>222</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>224</v>
       </c>
       <c r="F45" s="16" t="s">
         <v>35</v>
@@ -4356,7 +4338,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -4376,31 +4358,31 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="E47" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="15" t="s">
+      <c r="F47" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="J47" s="17">
         <v>45877</v>
@@ -4416,39 +4398,39 @@
         <v>45935</v>
       </c>
       <c r="O47" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P47" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="C48" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="D48" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="E48" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>234</v>
-      </c>
       <c r="F48" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H48" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J48" s="17">
         <v>45877</v>
@@ -4464,39 +4446,39 @@
         <v>45935</v>
       </c>
       <c r="O48" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P48" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="C49" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="D49" s="15" t="s">
-        <v>238</v>
-      </c>
       <c r="E49" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F49" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H49" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J49" s="17">
         <v>45877</v>
@@ -4512,39 +4494,39 @@
         <v>45935</v>
       </c>
       <c r="O49" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P49" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="C50" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="E50" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="E50" s="15" t="s">
-        <v>243</v>
-      </c>
       <c r="F50" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J50" s="17">
         <v>45877</v>
@@ -4560,39 +4542,39 @@
         <v>45935</v>
       </c>
       <c r="O50" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P50" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="C51" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="D51" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>247</v>
-      </c>
       <c r="F51" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H51" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J51" s="17">
         <v>45877</v>
@@ -4608,39 +4590,39 @@
         <v>45935</v>
       </c>
       <c r="O51" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P51" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="C52" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="D52" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="D52" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>251</v>
-      </c>
       <c r="F52" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H52" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J52" s="17">
         <v>45877</v>
@@ -4656,27 +4638,27 @@
         <v>45935</v>
       </c>
       <c r="O52" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P52" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="C53" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="D53" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="E53" s="15" t="s">
         <v>255</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>256</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>35</v>
@@ -4688,7 +4670,7 @@
         <v>23</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J53" s="17">
         <v>45877</v>
@@ -4708,19 +4690,19 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="B54" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="C54" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="D54" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="E54" s="15" t="s">
         <v>261</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>262</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>35</v>
@@ -4732,7 +4714,7 @@
         <v>23</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="J54" s="17">
         <v>45877</v>
@@ -4748,39 +4730,39 @@
         <v>45935</v>
       </c>
       <c r="O54" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P54" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="D55" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="E55" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>268</v>
-      </c>
       <c r="F55" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H55" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J55" s="17">
         <v>45877</v>
@@ -4796,39 +4778,39 @@
         <v>45935</v>
       </c>
       <c r="O55" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P55" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="D56" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="E56" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="D56" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="F56" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="J56" s="17">
         <v>45877</v>
@@ -4844,27 +4826,27 @@
         <v>45935</v>
       </c>
       <c r="O56" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P56" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="D57" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="E57" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>277</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>35</v>
@@ -4876,7 +4858,7 @@
         <v>23</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>278</v>
+        <v>228</v>
       </c>
       <c r="J57" s="17">
         <v>45877</v>
@@ -4892,39 +4874,39 @@
         <v>45935</v>
       </c>
       <c r="O57" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P57" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>282</v>
-      </c>
       <c r="F58" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H58" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J58" s="17">
         <v>45877</v>
@@ -4940,39 +4922,39 @@
         <v>45935</v>
       </c>
       <c r="O58" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P58" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>286</v>
-      </c>
       <c r="E59" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H59" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J59" s="17">
         <v>45877</v>
@@ -4988,39 +4970,39 @@
         <v>45935</v>
       </c>
       <c r="O59" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P59" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="E60" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="B60" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>290</v>
-      </c>
       <c r="F60" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J60" s="17">
         <v>45877</v>
@@ -5036,39 +5018,39 @@
         <v>45935</v>
       </c>
       <c r="O60" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P60" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="B61" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>294</v>
-      </c>
       <c r="F61" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H61" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J61" s="17">
         <v>45877</v>
@@ -5084,39 +5066,39 @@
         <v>45935</v>
       </c>
       <c r="O61" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P61" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F62" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H62" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J62" s="17">
         <v>45877</v>
@@ -5132,27 +5114,27 @@
         <v>45935</v>
       </c>
       <c r="O62" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P62" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E63" s="15" t="s">
         <v>297</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>300</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>35</v>
@@ -5164,7 +5146,7 @@
         <v>23</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J63" s="17">
         <v>45877</v>
@@ -5184,7 +5166,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -5212,19 +5194,19 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="D65" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="E65" s="15" t="s">
         <v>304</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>307</v>
       </c>
       <c r="F65" s="16" t="s">
         <v>35</v>
@@ -5236,7 +5218,7 @@
         <v>23</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J65" s="17">
         <v>45877</v>
@@ -5252,27 +5234,27 @@
         <v>45935</v>
       </c>
       <c r="O65" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P65" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>309</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>313</v>
       </c>
       <c r="F66" s="16" t="s">
         <v>35</v>
@@ -5284,7 +5266,7 @@
         <v>23</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J66" s="17">
         <v>45877</v>
@@ -5304,19 +5286,19 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>315</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="E67" s="15" t="s">
-        <v>319</v>
       </c>
       <c r="F67" s="16" t="s">
         <v>35</v>
@@ -5328,7 +5310,7 @@
         <v>23</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J67" s="17">
         <v>45877</v>
@@ -5344,27 +5326,27 @@
         <v>45935</v>
       </c>
       <c r="O67" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P67" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>320</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>324</v>
       </c>
       <c r="F68" s="16" t="s">
         <v>35</v>
@@ -5376,7 +5358,7 @@
         <v>23</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J68" s="17">
         <v>45877</v>
@@ -5392,27 +5374,27 @@
         <v>45935</v>
       </c>
       <c r="O68" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P68" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>325</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>329</v>
       </c>
       <c r="F69" s="16" t="s">
         <v>35</v>
@@ -5424,7 +5406,7 @@
         <v>23</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J69" s="17">
         <v>45877</v>
@@ -5440,27 +5422,27 @@
         <v>45935</v>
       </c>
       <c r="O69" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P69" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F70" s="16" t="s">
         <v>35</v>
@@ -5472,7 +5454,7 @@
         <v>23</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J70" s="17">
         <v>45877</v>
@@ -5488,27 +5470,27 @@
         <v>45935</v>
       </c>
       <c r="O70" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P70" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="E71" s="15" t="s">
         <v>334</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>338</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>35</v>
@@ -5520,7 +5502,7 @@
         <v>23</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J71" s="17">
         <v>45877</v>
@@ -5536,27 +5518,27 @@
         <v>45935</v>
       </c>
       <c r="O71" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P71" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="E72" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>343</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>35</v>
@@ -5568,7 +5550,7 @@
         <v>23</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J72" s="17">
         <v>45877</v>
@@ -5584,27 +5566,27 @@
         <v>45935</v>
       </c>
       <c r="O72" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P72" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>344</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>348</v>
       </c>
       <c r="F73" s="16" t="s">
         <v>35</v>
@@ -5616,7 +5598,7 @@
         <v>23</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J73" s="17">
         <v>45877</v>
@@ -5632,27 +5614,27 @@
         <v>45935</v>
       </c>
       <c r="O73" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P73" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>353</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>35</v>
@@ -5664,7 +5646,7 @@
         <v>23</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J74" s="17">
         <v>45877</v>
@@ -5680,27 +5662,27 @@
         <v>45935</v>
       </c>
       <c r="O74" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P74" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>354</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>358</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>35</v>
@@ -5712,7 +5694,7 @@
         <v>23</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J75" s="17">
         <v>45877</v>
@@ -5728,27 +5710,27 @@
         <v>45935</v>
       </c>
       <c r="O75" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P75" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>35</v>
@@ -5760,7 +5742,7 @@
         <v>23</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J76" s="17">
         <v>45877</v>
@@ -5776,27 +5758,27 @@
         <v>45935</v>
       </c>
       <c r="O76" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P76" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E77" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>35</v>
@@ -5808,7 +5790,7 @@
         <v>23</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J77" s="17">
         <v>45877</v>
@@ -5824,27 +5806,27 @@
         <v>45935</v>
       </c>
       <c r="O77" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P77" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E78" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="E78" s="15" t="s">
-        <v>372</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>35</v>
@@ -5856,7 +5838,7 @@
         <v>23</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="J78" s="17">
         <v>45877</v>
@@ -5872,15 +5854,15 @@
         <v>45935</v>
       </c>
       <c r="O78" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P78" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -5902,19 +5884,19 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="E80" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>375</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>378</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>35</v>
@@ -5942,27 +5924,27 @@
         <v>45935</v>
       </c>
       <c r="O80" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P80" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>35</v>
@@ -5990,39 +5972,39 @@
         <v>45935</v>
       </c>
       <c r="O81" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P81" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E82" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>387</v>
-      </c>
       <c r="F82" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="H82" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>388</v>
+        <v>24</v>
       </c>
       <c r="J82" s="17">
         <v>45877</v>
@@ -6038,27 +6020,27 @@
         <v>45935</v>
       </c>
       <c r="O82" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P82" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>35</v>
@@ -6086,27 +6068,27 @@
         <v>45935</v>
       </c>
       <c r="O83" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P83" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>35</v>
@@ -6134,27 +6116,27 @@
         <v>45935</v>
       </c>
       <c r="O84" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P84" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="22" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>35</v>
@@ -6166,7 +6148,7 @@
         <v>23</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J85" s="17">
         <v>45877</v>
@@ -6186,19 +6168,19 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="22" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>35</v>
@@ -6210,7 +6192,7 @@
         <v>23</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J86" s="17">
         <v>45877</v>
@@ -6230,19 +6212,19 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>35</v>
@@ -6254,7 +6236,7 @@
         <v>23</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J87" s="17">
         <v>45877</v>
@@ -6274,19 +6256,19 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F88" s="16" t="s">
         <v>35</v>
@@ -6314,27 +6296,27 @@
         <v>45935</v>
       </c>
       <c r="O88" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P88" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C89" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="D89" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="D89" s="15" t="s">
-        <v>421</v>
-      </c>
       <c r="E89" s="15" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F89" s="16" t="s">
         <v>35</v>
@@ -6346,7 +6328,7 @@
         <v>23</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="J89" s="17">
         <v>45877</v>
@@ -6366,19 +6348,19 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>35</v>
@@ -6406,27 +6388,27 @@
         <v>45935</v>
       </c>
       <c r="O90" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P90" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="22" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>35</v>
@@ -6438,7 +6420,7 @@
         <v>23</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J91" s="17">
         <v>45877</v>
@@ -6458,19 +6440,19 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="22" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>35</v>
@@ -6482,7 +6464,7 @@
         <v>23</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J92" s="17">
         <v>45877</v>
@@ -6502,19 +6484,19 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>35</v>
@@ -6526,7 +6508,7 @@
         <v>23</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J93" s="17">
         <v>45877</v>
@@ -6546,19 +6528,19 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="22" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>35</v>
@@ -6570,7 +6552,7 @@
         <v>23</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="J94" s="17">
         <v>45877</v>
@@ -6586,15 +6568,15 @@
         <v>45935</v>
       </c>
       <c r="O94" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P94" s="11">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -6613,31 +6595,31 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H96" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J96" s="17">
         <v>45881</v>
@@ -6653,39 +6635,39 @@
         <v>45987</v>
       </c>
       <c r="O96" s="23">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P96" s="24">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="F97" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H97" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J97" s="17">
         <v>45881</v>
@@ -6701,39 +6683,39 @@
         <v>45987</v>
       </c>
       <c r="O97" s="23">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P97" s="24">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F98" s="16" t="s">
         <v>35</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H98" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J98" s="17">
         <v>45881</v>
@@ -6749,27 +6731,27 @@
         <v>45987</v>
       </c>
       <c r="O98" s="23">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P98" s="24">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F99" s="16" t="s">
         <v>35</v>
@@ -6781,7 +6763,7 @@
         <v>23</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J99" s="17">
         <v>45881</v>
@@ -6800,19 +6782,19 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F100" s="16" t="s">
         <v>35</v>
@@ -6824,7 +6806,7 @@
         <v>23</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J100" s="17">
         <v>45881</v>
@@ -6843,19 +6825,19 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F101" s="16" t="s">
         <v>35</v>
@@ -6867,7 +6849,7 @@
         <v>23</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J101" s="17">
         <v>45881</v>
@@ -6886,19 +6868,19 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F102" s="16" t="s">
         <v>35</v>
@@ -6910,7 +6892,7 @@
         <v>23</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J102" s="17">
         <v>45881</v>
@@ -6929,19 +6911,19 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F103" s="16" t="s">
         <v>35</v>
@@ -6953,7 +6935,7 @@
         <v>23</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J103" s="17">
         <v>45881</v>
@@ -6972,19 +6954,19 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F104" s="16" t="s">
         <v>35</v>
@@ -6996,7 +6978,7 @@
         <v>23</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J104" s="17">
         <v>45881</v>
@@ -7015,19 +6997,19 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F105" s="16" t="s">
         <v>35</v>
@@ -7039,7 +7021,7 @@
         <v>23</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J105" s="17">
         <v>45881</v>
@@ -7058,19 +7040,19 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F106" s="16" t="s">
         <v>35</v>
@@ -7082,7 +7064,7 @@
         <v>23</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J106" s="17">
         <v>45881</v>
@@ -7101,19 +7083,19 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F107" s="16" t="s">
         <v>35</v>
@@ -7125,7 +7107,7 @@
         <v>23</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J107" s="17">
         <v>45881</v>
@@ -7144,19 +7126,19 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F108" s="16" t="s">
         <v>35</v>
@@ -7168,7 +7150,7 @@
         <v>23</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J108" s="17">
         <v>45881</v>
@@ -7187,19 +7169,19 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F109" s="16" t="s">
         <v>35</v>
@@ -7211,7 +7193,7 @@
         <v>23</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J109" s="17">
         <v>45881</v>
@@ -7230,19 +7212,19 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F110" s="16" t="s">
         <v>35</v>
@@ -7254,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J110" s="17">
         <v>45881</v>
@@ -7273,19 +7255,19 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F111" s="16" t="s">
         <v>35</v>
@@ -7297,7 +7279,7 @@
         <v>23</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J111" s="17">
         <v>45881</v>
@@ -7316,19 +7298,19 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F112" s="16" t="s">
         <v>35</v>
@@ -7340,7 +7322,7 @@
         <v>23</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J112" s="17">
         <v>45881</v>
@@ -7359,19 +7341,19 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="F113" s="16" t="s">
         <v>35</v>
@@ -7383,7 +7365,7 @@
         <v>23</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J113" s="17">
         <v>45881</v>
@@ -7402,19 +7384,19 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F114" s="16" t="s">
         <v>35</v>
@@ -7426,7 +7408,7 @@
         <v>23</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J114" s="17">
         <v>45881</v>
@@ -7445,7 +7427,7 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
@@ -7472,19 +7454,19 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="F116" s="16" t="s">
         <v>35</v>
@@ -7496,7 +7478,7 @@
         <v>23</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>536</v>
+        <v>80</v>
       </c>
       <c r="J116" s="17">
         <v>45881</v>
@@ -7512,27 +7494,27 @@
         <v>45987</v>
       </c>
       <c r="O116" s="23">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
       <c r="P116" s="24">
-        <v>46191.92044299768</v>
+        <v>46191.95268071759</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F117" s="16" t="s">
         <v>35</v>
@@ -7544,7 +7526,7 @@
         <v>23</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J117" s="17">
         <v>45881</v>
@@ -7563,19 +7545,19 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F118" s="16" t="s">
         <v>35</v>
@@ -7587,7 +7569,7 @@
         <v>23</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J118" s="17">
         <v>45881</v>
@@ -7606,19 +7588,19 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F119" s="16" t="s">
         <v>35</v>
@@ -7630,7 +7612,7 @@
         <v>23</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J119" s="17">
         <v>45881</v>
@@ -7649,19 +7631,19 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F120" s="16" t="s">
         <v>35</v>
@@ -7673,7 +7655,7 @@
         <v>23</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J120" s="17">
         <v>45881</v>
@@ -7692,19 +7674,19 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F121" s="16" t="s">
         <v>35</v>
@@ -7716,7 +7698,7 @@
         <v>23</v>
       </c>
       <c r="I121" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J121" s="17">
         <v>45881</v>
@@ -7735,19 +7717,19 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F122" s="16" t="s">
         <v>35</v>
@@ -7759,7 +7741,7 @@
         <v>23</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J122" s="17">
         <v>45881</v>
@@ -7778,19 +7760,19 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="F123" s="16" t="s">
         <v>35</v>
@@ -7802,7 +7784,7 @@
         <v>23</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J123" s="17">
         <v>45881</v>
@@ -7821,19 +7803,19 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F124" s="16" t="s">
         <v>35</v>
@@ -7845,7 +7827,7 @@
         <v>23</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J124" s="17">
         <v>45881</v>
@@ -7864,19 +7846,19 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F125" s="16" t="s">
         <v>35</v>
@@ -7888,7 +7870,7 @@
         <v>23</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J125" s="17">
         <v>45881</v>
@@ -7907,19 +7889,19 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F126" s="16" t="s">
         <v>35</v>
@@ -7931,7 +7913,7 @@
         <v>23</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J126" s="17">
         <v>45881</v>
@@ -7950,19 +7932,19 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F127" s="16" t="s">
         <v>35</v>
@@ -7974,7 +7956,7 @@
         <v>23</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J127" s="17">
         <v>45881</v>
@@ -7993,19 +7975,19 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F128" s="16" t="s">
         <v>35</v>
@@ -8017,7 +7999,7 @@
         <v>23</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J128" s="17">
         <v>45881</v>
@@ -8036,19 +8018,19 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F129" s="16" t="s">
         <v>35</v>
@@ -8060,7 +8042,7 @@
         <v>23</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J129" s="17">
         <v>45881</v>
@@ -8079,19 +8061,19 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>35</v>
@@ -8103,7 +8085,7 @@
         <v>23</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J130" s="17">
         <v>45881</v>
@@ -8122,19 +8104,19 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F131" s="16" t="s">
         <v>35</v>
@@ -8146,7 +8128,7 @@
         <v>23</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J131" s="17">
         <v>45881</v>

--- a/reports/test-cases-filled.xlsx
+++ b/reports/test-cases-filled.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="1023">
   <si>
     <t xml:space="preserve">                                                                                          </t>
   </si>
@@ -297,7 +297,7 @@
     <t>Access is granted to all instance level functions</t>
   </si>
   <si>
-    <t>Fail - All core sidebar entries (Users, Orders, Roles, Products, Locations) are available, and navigating to Users and Orders loads their pages. did not behave as expected (runtime: Error: Sidebar entry "Users" should be available)</t>
+    <t>Pass - All core sidebar entries (Users, Orders, Roles, Products, Locations) are available, and navigating to Users and Orders loads their pages.</t>
   </si>
   <si>
     <t xml:space="preserve">USER MANAGEMENT </t>
@@ -319,7 +319,7 @@
     <t>- List of users displayed.- Users show key attributes (name, email, role, country, status, association).</t>
   </si>
   <si>
-    <t>Pending - The Users page shows a populated table with name, email, role and status columns. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - The Users page shows a populated table with name, email, role and status columns.</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC02</t>
@@ -339,7 +339,7 @@
     <t>- Matching users returned.- No irrelevant users displayed.</t>
   </si>
   <si>
-    <t>Pending - Searching a term taken from the first row returned matching rows that contain that term. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Searching a term taken from the first row returned matching rows that contain that term.</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC03</t>
@@ -359,7 +359,7 @@
     <t>- Only users from selected country are displayed.</t>
   </si>
   <si>
-    <t>Pending - the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - automated check passed against the live portal.</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC04</t>
@@ -393,6 +393,9 @@
     <t>- Only users with selected status are shown.</t>
   </si>
   <si>
+    <t>Fail - No status filter control is present on the Users list in this build. (runtime: Error: No status filter control is present on the Users list)</t>
+  </si>
+  <si>
     <t>IA-FM01-F15-TC06</t>
   </si>
   <si>
@@ -409,7 +412,7 @@
     <t>- Full user profile displayed.- Includes personal details, business info, roles, associations, activity summary.</t>
   </si>
   <si>
-    <t>Pending - Opening a user via View navigated to the profile route and displayed identifying details (email, phone, role, status, name). Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Opening a user via View navigated to the profile route and displayed identifying details (email, phone, role, status, name).</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC07</t>
@@ -445,7 +448,7 @@
     <t>System block editing of user's phone number and email</t>
   </si>
   <si>
-    <t>Pending - On the user profile, phone and email have no enabled editor, confirming they are read-only as required. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - On the user profile, phone and email have no enabled editor, confirming they are read-only as required.</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC10</t>
@@ -552,7 +555,7 @@
     <t>Role created successfully</t>
   </si>
   <si>
-    <t>Pending - Created a throwaway role via Add Role and confirmed it appears in the roles table (cleaned up by deactivation afterwards). Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Fail - List view is capped at the first 10 rows (it reads "Showing 1-10 of N") but exposes no pagination controls and no search box, so records beyond the first 10 are unreachable. A newly created record sorts to the end of the list and therefore cannot be viewed, edited, or deactivated through the UI. (runtime: Error: expect(locator).toBeVisible() failed)</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC02</t>
@@ -567,7 +570,7 @@
     <t>Validation error displayed</t>
   </si>
   <si>
-    <t>Pending - Submitting an empty role name was rejected: the modal stayed open / a validation error showed / no new row was added. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Submitting an empty role name was rejected: the modal stayed open / a validation error showed / no new row was added.</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC03</t>
@@ -585,7 +588,7 @@
     <t>System prevents duplication</t>
   </si>
   <si>
-    <t>Pending - Re-using an existing role name was prevented; no duplicate row was created. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Re-using an existing role name was prevented; no duplicate row was created.</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC04</t>
@@ -604,7 +607,7 @@
     <t>Changes saved successfully</t>
   </si>
   <si>
-    <t>Pending - Renamed the role then reverted it; the updated name appeared in the table, confirming edits persist. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Fail - List view is capped at the first 10 rows (it reads "Showing 1-10 of N") but exposes no pagination controls and no search box, so records beyond the first 10 are unreachable. A newly created record sorts to the end of the list and therefore cannot be viewed, edited, or deactivated through the UI. (runtime: Error: Temp role from TC01 should exist)</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC05</t>
@@ -619,9 +622,6 @@
     <t>All permissions and metadata visible</t>
   </si>
   <si>
-    <t>Pending - Opened the role editor and confirmed the Role Name and Active fields are displayed. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
-  </si>
-  <si>
     <t>IA-FM01-F03-TC06</t>
   </si>
   <si>
@@ -637,7 +637,7 @@
     <t>Role marked inactive</t>
   </si>
   <si>
-    <t>Pending - Unchecked Active and saved; re-opening the role confirmed it now reads inactive. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Fail - List view is capped at the first 10 rows (it reads "Showing 1-10 of N") but exposes no pagination controls and no search box, so records beyond the first 10 are unreachable. A newly created record sorts to the end of the list and therefore cannot be viewed, edited, or deactivated through the UI. (runtime: Test timeout of 30000ms exceeded.)</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC07</t>
@@ -653,9 +653,6 @@
   </si>
   <si>
     <t>Role restored</t>
-  </si>
-  <si>
-    <t>Pending - Re-checked Active and saved; re-opening the role confirmed it now reads active again. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC08</t>
@@ -671,6 +668,9 @@
   </si>
   <si>
     <t>Permission assigned</t>
+  </si>
+  <si>
+    <t>Fail - The role editor exposes only an Active toggle - no permission-assignment UI exists in this build. (runtime: Test timeout of 30000ms exceeded.)</t>
   </si>
   <si>
     <t>IA-FM01-F03-TC09</t>
@@ -867,9 +867,6 @@
     <t xml:space="preserve"> level created successfully</t>
   </si>
   <si>
-    <t>Fail - Created a location level with no parent via Add Level and confirmed it appears in the list (cleaned up by deactivation afterwards). did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC02</t>
   </si>
   <si>
@@ -889,9 +886,6 @@
     <t>Location level created and linked to parent location level</t>
   </si>
   <si>
-    <t>Fail - Created a child location level linked to parent ID 1 and confirmed it appears in the list. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC03</t>
   </si>
   <si>
@@ -905,7 +899,7 @@
 2. Save</t>
   </si>
   <si>
-    <t>Fail - Submitting a level with no name was rejected: the modal stayed open / a validation error showed / no new row was added. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Pass - Submitting a level with no name was rejected: the modal stayed open / a validation error showed / no new row was added.</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC04</t>
@@ -923,7 +917,7 @@
     <t>Duplicate prevented</t>
   </si>
   <si>
-    <t>Fail - Re-using an existing level name was prevented; no duplicate was created. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Pass - Re-using an existing level name was prevented; no duplicate was created.</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC05</t>
@@ -938,9 +932,6 @@
     <t>Level marked inactive</t>
   </si>
   <si>
-    <t>Fail - Deactivated the temp level via the Active toggle and confirmed it reads unchecked on re-open. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC06</t>
   </si>
   <si>
@@ -953,7 +944,7 @@
     <t>Level reactivated</t>
   </si>
   <si>
-    <t>Fail - Reactivated the temp level and confirmed the Active toggle reads checked on re-open. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Pending - Reactivated the temp level and confirmed the Active toggle reads checked on re-open. Skipped at runtime: precondition not met</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC07</t>
@@ -989,7 +980,7 @@
     <t>Inactive not visible</t>
   </si>
   <si>
-    <t>Fail - After a level is deactivated it still appears in the default Location Levels list; inactive entries are not hidden. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Pending - skipped at runtime: precondition not met</t>
   </si>
   <si>
     <t>IA-FM01-F10-TCDEL1</t>
@@ -1029,9 +1020,6 @@
   </si>
   <si>
     <t>Location created</t>
-  </si>
-  <si>
-    <t>Fail - Created a parent location with no parent and confirmed it appears in the locations table. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC10</t>
@@ -1054,9 +1042,6 @@
     <t>Location created and linked to the parent location</t>
   </si>
   <si>
-    <t>Fail - Created a child location linked to parent ID 1 and confirmed it appears in the table. did not behave as expected (runtime: Error: expect(locator).toBeVisible() failed)</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC11</t>
   </si>
   <si>
@@ -1069,9 +1054,6 @@
     <t>Location level not listed on options</t>
   </si>
   <si>
-    <t>Fail - The location form uses a free-text Level ID with no options list, so exclusion of inactive levels cannot be enforced or verified. (runtime: Error: expect(locator).toBeVisible() failed)</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC12</t>
   </si>
   <si>
@@ -1084,7 +1066,7 @@
     <t>Validation error</t>
   </si>
   <si>
-    <t>Pending - Submitting a location with missing fields was rejected: the modal stayed open / a validation error showed / no new row was added. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Submitting a location with missing fields was rejected: the modal stayed open / a validation error showed / no new row was added.</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC13</t>
@@ -1099,7 +1081,7 @@
     <t>1. Create with same name</t>
   </si>
   <si>
-    <t>Pending - Re-using an existing location name was prevented; no duplicate was created. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Re-using an existing location name was prevented; no duplicate was created.</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC14</t>
@@ -1115,9 +1097,6 @@
     <t>Parent updated</t>
   </si>
   <si>
-    <t>Pending - Set the location's Parent ID then reverted it; the update saved without error. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC15</t>
   </si>
   <si>
@@ -1130,16 +1109,13 @@
     <t>Location inactive</t>
   </si>
   <si>
-    <t>Pending - Deactivated the temp location via the Active toggle and saved. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
-  </si>
-  <si>
     <t>IA-FM01-F10-TC16</t>
   </si>
   <si>
     <t>Activate Location</t>
   </si>
   <si>
-    <t>Pending - Reactivated the temp location and confirmed the Active toggle reads checked on re-open. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pending - Reactivated the temp location and confirmed the Active toggle reads checked on re-open. Skipped at runtime: precondition not met</t>
   </si>
   <si>
     <t>IA-FM01-F10-TC17</t>
@@ -1197,7 +1173,7 @@
     <t>All users exported</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC15</t>
@@ -1233,7 +1209,7 @@
     <t>Name includes date/time</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build, so the file name cannot be checked. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build, so the file name cannot be checked. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC17</t>
@@ -1251,7 +1227,7 @@
     <t>No corruption</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build, so no file can be produced or opened. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build, so no file can be produced or opened. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC18</t>
@@ -1269,7 +1245,7 @@
     <t>Correct column names</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build, so no exported header row exists to validate. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build, so no exported header row exists to validate. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC19</t>
@@ -1284,7 +1260,7 @@
     <t>Counts match</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build, so exported counts cannot be compared. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build, so exported counts cannot be compared. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC20</t>
@@ -1302,7 +1278,7 @@
     <t>Correct data types</t>
   </si>
   <si>
-    <t>Fail - No export/download control is present on the Users list in this build, so exported data formatting cannot be checked. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control is present on the Users list in this build, so exported data formatting cannot be checked. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC21</t>
@@ -1321,7 +1297,7 @@
     <t>Only selected country users</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor a location/country filter) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor a location/country filter) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC22</t>
@@ -1340,7 +1316,7 @@
     <t>Correct subset exported</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor an association filter) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor an association filter) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC23</t>
@@ -1359,7 +1335,7 @@
     <t>Role-specific users exported</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor a role filter) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor a role filter) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC24</t>
@@ -1378,7 +1354,7 @@
     <t>Only matching users</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor a status filter) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor a status filter) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC25</t>
@@ -1394,7 +1370,7 @@
 2. Export</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor a date-range filter) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor a date-range filter) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC26</t>
@@ -1413,7 +1389,7 @@
     <t>All conditions respected</t>
   </si>
   <si>
-    <t>Fail - No export/download control (nor filter controls) is present on the Users list in this build. (runtime: Error: expect(locator).toBeVisible() failed)</t>
+    <t>Fail - No export/download control (nor filter controls) is present on the Users list in this build. (runtime: Error: No export/download control is present on the Users list)</t>
   </si>
   <si>
     <t>IA-FM01-F15-TC27</t>
@@ -1432,6 +1408,9 @@
     <t>Empty file or warning</t>
   </si>
   <si>
+    <t>Fail - No export/download control is present on the Users list in this build, so an empty-result export cannot be exercised. (runtime: Error: No export/download control is present on the Users list)</t>
+  </si>
+  <si>
     <t>ASSOCIATION MANAGEMENT</t>
   </si>
   <si>
@@ -1484,9 +1463,6 @@
   </si>
   <si>
     <t>- Only associations from selected country displayed.</t>
-  </si>
-  <si>
-    <t>Pass - automated check passed against the live portal.</t>
   </si>
   <si>
     <t>IA-CM05-F01-TC04</t>
@@ -1627,7 +1603,7 @@
     <t>- List of members displayed with status.</t>
   </si>
   <si>
-    <t>Pass - Opened an association profile and confirmed a members section/list is present.</t>
+    <t>Fail - Opened an association profile and confirmed a members section/list is present. did not behave as expected (runtime: Error: No members section/list is present on the association profile)</t>
   </si>
   <si>
     <t>IA-CM05-F01-TC13</t>
@@ -2877,7 +2853,7 @@
     <t>Order displayed with correct details</t>
   </si>
   <si>
-    <t>Pending - Orders page renders; filtering to Pending shows the orders table with order/status/date/total columns. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Orders page renders; filtering to Pending shows the orders table with order/status/date/total columns.</t>
   </si>
   <si>
     <t>IA-CM02-F08-TC02</t>
@@ -2895,7 +2871,7 @@
     <t>Product, unit, price, totals accurate</t>
   </si>
   <si>
-    <t>Pending - Opened an order via View and confirmed the detail page shows product, quantity, price and total. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - Opened an order via View and confirmed the detail page shows product, quantity, price and total.</t>
   </si>
   <si>
     <t>IA-CM02-F08-TC03</t>
@@ -2913,7 +2889,7 @@
     <t>Status = Pending</t>
   </si>
   <si>
-    <t>Pending - The Pending filter lists orders whose status reads Pending, confirming the default status. Not verified this run: the test session expired (redirected to sign-in / setup hook timed out) before the check ran; re-run with a fresh login.</t>
+    <t>Pass - The Pending filter lists orders whose status reads Pending, confirming the default status.</t>
   </si>
   <si>
     <t>IA-CM02-F08-TC04</t>
@@ -3305,8 +3281,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="166" formatCode="d&quot;-&quot;mmm&quot;-&quot;yy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -3646,7 +3622,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3666,7 +3642,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3691,7 +3667,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3759,7 +3735,7 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3780,10 +3756,10 @@
     <xf numFmtId="166" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4490,10 +4466,10 @@
         <v>45935</v>
       </c>
       <c r="O13" s="52">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P13" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -4548,10 +4524,10 @@
         <v>45935</v>
       </c>
       <c r="O14" s="52">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P14" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -4772,10 +4748,10 @@
       <c r="M18" s="40"/>
       <c r="N18" s="46"/>
       <c r="O18" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P18" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -4866,10 +4842,10 @@
         <v>45935</v>
       </c>
       <c r="O20" s="52">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P20" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
@@ -4924,10 +4900,10 @@
         <v>45935</v>
       </c>
       <c r="O21" s="52">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P21" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
@@ -4960,7 +4936,7 @@
         <v>51</v>
       </c>
       <c r="G22" s="50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H22" s="50" t="s">
         <v>38</v>
@@ -4982,10 +4958,10 @@
         <v>45935</v>
       </c>
       <c r="O22" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P22" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
@@ -5050,7 +5026,7 @@
         <v>51</v>
       </c>
       <c r="G24" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H24" s="50" t="s">
         <v>38</v>
@@ -5071,8 +5047,12 @@
       <c r="N24" s="51">
         <v>45935</v>
       </c>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
+      <c r="O24" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P24" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
@@ -5104,7 +5084,7 @@
         <v>51</v>
       </c>
       <c r="G25" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="50" t="s">
         <v>38</v>
@@ -5125,8 +5105,12 @@
       <c r="N25" s="51">
         <v>45935</v>
       </c>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
+      <c r="O25" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P25" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
@@ -5158,7 +5142,7 @@
         <v>51</v>
       </c>
       <c r="G26" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="50" t="s">
         <v>38</v>
@@ -5179,8 +5163,12 @@
       <c r="N26" s="51">
         <v>45935</v>
       </c>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
+      <c r="O26" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P26" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
@@ -5212,7 +5200,7 @@
         <v>51</v>
       </c>
       <c r="G27" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="50" t="s">
         <v>38</v>
@@ -5233,8 +5221,12 @@
       <c r="N27" s="51">
         <v>45935</v>
       </c>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
+      <c r="O27" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P27" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
@@ -5266,13 +5258,13 @@
         <v>51</v>
       </c>
       <c r="G28" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="J28" s="51">
         <v>45877</v>
@@ -5287,8 +5279,12 @@
       <c r="N28" s="51">
         <v>45935</v>
       </c>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
+      <c r="O28" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P28" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
@@ -5302,31 +5298,31 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I29" s="45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J29" s="51">
         <v>45877</v>
@@ -5341,8 +5337,12 @@
       <c r="N29" s="51">
         <v>45935</v>
       </c>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
+      <c r="O29" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P29" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
@@ -5356,19 +5356,19 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" s="49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F30" s="50" t="s">
         <v>51</v>
@@ -5380,7 +5380,7 @@
         <v>38</v>
       </c>
       <c r="I30" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J30" s="51">
         <v>45877</v>
@@ -5410,31 +5410,31 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="48" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C31" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E31" s="49" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H31" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J31" s="51">
         <v>45877</v>
@@ -5449,8 +5449,12 @@
       <c r="N31" s="51">
         <v>45935</v>
       </c>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
+      <c r="O31" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P31" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
@@ -5464,19 +5468,19 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E32" s="49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>51</v>
@@ -5488,7 +5492,7 @@
         <v>38</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J32" s="51">
         <v>45877</v>
@@ -5518,19 +5522,19 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>51</v>
@@ -5542,7 +5546,7 @@
         <v>38</v>
       </c>
       <c r="I33" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J33" s="51">
         <v>45877</v>
@@ -5572,19 +5576,19 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34" s="49" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>51</v>
@@ -5596,7 +5600,7 @@
         <v>38</v>
       </c>
       <c r="I34" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J34" s="51">
         <v>45877</v>
@@ -5626,19 +5630,19 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E35" s="49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F35" s="50" t="s">
         <v>51</v>
@@ -5650,7 +5654,7 @@
         <v>38</v>
       </c>
       <c r="I35" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J35" s="51">
         <v>45877</v>
@@ -5680,19 +5684,19 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F36" s="50"/>
       <c r="G36" s="50" t="s">
@@ -5700,22 +5704,22 @@
       </c>
       <c r="H36" s="50"/>
       <c r="I36" s="45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J36" s="51"/>
       <c r="K36" s="47"/>
       <c r="L36" s="50"/>
       <c r="N36" s="51"/>
       <c r="O36" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P36" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B37" s="54"/>
       <c r="C37" s="54"/>
@@ -5745,31 +5749,31 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F38" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G38" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H38" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I38" s="45" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J38" s="51">
         <v>45877</v>
@@ -5784,8 +5788,12 @@
       <c r="N38" s="51">
         <v>45935</v>
       </c>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
+      <c r="O38" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P38" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
       <c r="S38" s="4"/>
@@ -5799,31 +5807,31 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H39" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I39" s="45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J39" s="51">
         <v>45877</v>
@@ -5838,8 +5846,12 @@
       <c r="N39" s="51">
         <v>45935</v>
       </c>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
+      <c r="O39" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P39" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
@@ -5853,31 +5865,31 @@
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E40" s="49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G40" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H40" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I40" s="45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J40" s="51">
         <v>45877</v>
@@ -5892,8 +5904,12 @@
       <c r="N40" s="51">
         <v>45935</v>
       </c>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
+      <c r="O40" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P40" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
@@ -5907,31 +5923,31 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G41" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H41" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I41" s="45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J41" s="51">
         <v>45877</v>
@@ -5946,8 +5962,12 @@
       <c r="N41" s="51">
         <v>45935</v>
       </c>
-      <c r="O41" s="45"/>
-      <c r="P41" s="45"/>
+      <c r="O41" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P41" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
@@ -5961,31 +5981,31 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E42" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G42" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H42" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I42" s="45" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="J42" s="51">
         <v>45877</v>
@@ -6000,8 +6020,12 @@
       <c r="N42" s="51">
         <v>45935</v>
       </c>
-      <c r="O42" s="45"/>
-      <c r="P42" s="45"/>
+      <c r="O42" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P42" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
@@ -6033,7 +6057,7 @@
         <v>51</v>
       </c>
       <c r="G43" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H43" s="50" t="s">
         <v>38</v>
@@ -6054,8 +6078,12 @@
       <c r="N43" s="51">
         <v>45935</v>
       </c>
-      <c r="O43" s="45"/>
-      <c r="P43" s="45"/>
+      <c r="O43" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P43" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
@@ -6087,13 +6115,13 @@
         <v>51</v>
       </c>
       <c r="G44" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H44" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I44" s="45" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J44" s="51">
         <v>45877</v>
@@ -6108,8 +6136,12 @@
       <c r="N44" s="51">
         <v>45935</v>
       </c>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
+      <c r="O44" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P44" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
@@ -6123,31 +6155,31 @@
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="C45" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="C45" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="D45" s="49" t="s">
+      <c r="E45" s="49" t="s">
         <v>203</v>
-      </c>
-      <c r="E45" s="49" t="s">
-        <v>204</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H45" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I45" s="45" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="J45" s="51">
         <v>45877</v>
@@ -6162,8 +6194,12 @@
       <c r="N45" s="51">
         <v>45935</v>
       </c>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
+      <c r="O45" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P45" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
@@ -6183,7 +6219,7 @@
         <v>206</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>207</v>
@@ -6195,13 +6231,13 @@
         <v>51</v>
       </c>
       <c r="G46" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H46" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I46" s="45" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="J46" s="51">
         <v>45877</v>
@@ -6216,8 +6252,12 @@
       <c r="N46" s="51">
         <v>45935</v>
       </c>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
+      <c r="O46" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P46" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
@@ -6249,13 +6289,13 @@
         <v>51</v>
       </c>
       <c r="G47" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H47" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I47" s="45" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="J47" s="51">
         <v>45877</v>
@@ -6270,8 +6310,12 @@
       <c r="N47" s="51">
         <v>45935</v>
       </c>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
+      <c r="O47" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P47" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
@@ -6303,13 +6347,13 @@
         <v>51</v>
       </c>
       <c r="G48" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H48" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I48" s="45" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="J48" s="51">
         <v>45877</v>
@@ -6324,8 +6368,12 @@
       <c r="N48" s="51">
         <v>45935</v>
       </c>
-      <c r="O48" s="45"/>
-      <c r="P48" s="45"/>
+      <c r="O48" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P48" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
@@ -6399,7 +6447,7 @@
         <v>226</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D50" s="49" t="s">
         <v>227</v>
@@ -6417,7 +6465,7 @@
         <v>38</v>
       </c>
       <c r="I50" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J50" s="51">
         <v>45877</v>
@@ -6471,7 +6519,7 @@
         <v>38</v>
       </c>
       <c r="I51" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J51" s="51">
         <v>45877</v>
@@ -6525,7 +6573,7 @@
         <v>38</v>
       </c>
       <c r="I52" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J52" s="51">
         <v>45877</v>
@@ -6798,10 +6846,10 @@
       <c r="L57" s="50"/>
       <c r="N57" s="51"/>
       <c r="O57" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P57" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
@@ -6842,7 +6890,7 @@
         <v>264</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D59" s="49" t="s">
         <v>265</v>
@@ -6860,7 +6908,7 @@
         <v>38</v>
       </c>
       <c r="I59" s="45" t="s">
-        <v>267</v>
+        <v>167</v>
       </c>
       <c r="J59" s="51">
         <v>45877</v>
@@ -6876,10 +6924,10 @@
         <v>45935</v>
       </c>
       <c r="O59" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P59" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
@@ -6894,19 +6942,19 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="B60" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="B60" s="49" t="s">
+      <c r="C60" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="C60" s="49" t="s">
+      <c r="D60" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="D60" s="49" t="s">
+      <c r="E60" s="49" t="s">
         <v>271</v>
-      </c>
-      <c r="E60" s="49" t="s">
-        <v>272</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>51</v>
@@ -6918,7 +6966,7 @@
         <v>38</v>
       </c>
       <c r="I60" s="45" t="s">
-        <v>273</v>
+        <v>167</v>
       </c>
       <c r="J60" s="51">
         <v>45877</v>
@@ -6934,10 +6982,10 @@
         <v>45935</v>
       </c>
       <c r="O60" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P60" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
@@ -6952,31 +7000,31 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="B61" s="49" t="s">
+      <c r="D61" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="D61" s="49" t="s">
-        <v>277</v>
-      </c>
       <c r="E61" s="49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G61" s="50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H61" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I61" s="45" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J61" s="51">
         <v>45877</v>
@@ -6992,10 +7040,10 @@
         <v>45935</v>
       </c>
       <c r="O61" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P61" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
@@ -7010,31 +7058,31 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="48" t="s">
+        <v>277</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="C62" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="B62" s="49" t="s">
+      <c r="D62" s="49" t="s">
         <v>280</v>
       </c>
-      <c r="C62" s="49" t="s">
+      <c r="E62" s="49" t="s">
         <v>281</v>
-      </c>
-      <c r="D62" s="49" t="s">
-        <v>282</v>
-      </c>
-      <c r="E62" s="49" t="s">
-        <v>283</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G62" s="50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H62" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I62" s="45" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J62" s="51">
         <v>45877</v>
@@ -7050,10 +7098,10 @@
         <v>45935</v>
       </c>
       <c r="O62" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P62" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
@@ -7068,19 +7116,19 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="B63" s="49" t="s">
+        <v>284</v>
+      </c>
+      <c r="C63" s="49" t="s">
         <v>285</v>
-      </c>
-      <c r="B63" s="49" t="s">
-        <v>286</v>
-      </c>
-      <c r="C63" s="49" t="s">
-        <v>287</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>192</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>51</v>
@@ -7092,7 +7140,7 @@
         <v>38</v>
       </c>
       <c r="I63" s="45" t="s">
-        <v>289</v>
+        <v>167</v>
       </c>
       <c r="J63" s="51">
         <v>45877</v>
@@ -7108,10 +7156,10 @@
         <v>45935</v>
       </c>
       <c r="O63" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P63" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
@@ -7126,31 +7174,31 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="48" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D64" s="49" t="s">
         <v>198</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G64" s="50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H64" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I64" s="45" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J64" s="51">
         <v>45877</v>
@@ -7165,12 +7213,8 @@
       <c r="N64" s="51">
         <v>45935</v>
       </c>
-      <c r="O64" s="45">
-        <v>46192.964436180555</v>
-      </c>
-      <c r="P64" s="45">
-        <v>46192.964436180555</v>
-      </c>
+      <c r="O64" s="45"/>
+      <c r="P64" s="45"/>
       <c r="Q64" s="4"/>
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
@@ -7184,19 +7228,19 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="48" t="s">
+        <v>292</v>
+      </c>
+      <c r="B65" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="D65" s="49" t="s">
         <v>295</v>
       </c>
-      <c r="B65" s="49" t="s">
+      <c r="E65" s="49" t="s">
         <v>296</v>
-      </c>
-      <c r="C65" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D65" s="49" t="s">
-        <v>298</v>
-      </c>
-      <c r="E65" s="49" t="s">
-        <v>299</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>51</v>
@@ -7208,7 +7252,7 @@
         <v>38</v>
       </c>
       <c r="I65" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J65" s="51">
         <v>45877</v>
@@ -7238,31 +7282,31 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B66" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="C66" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="D66" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="B66" s="49" t="s">
+      <c r="E66" s="49" t="s">
         <v>302</v>
-      </c>
-      <c r="C66" s="49" t="s">
-        <v>303</v>
-      </c>
-      <c r="D66" s="49" t="s">
-        <v>304</v>
-      </c>
-      <c r="E66" s="49" t="s">
-        <v>305</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G66" s="50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H66" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I66" s="45" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J66" s="51">
         <v>45877</v>
@@ -7277,12 +7321,8 @@
       <c r="N66" s="51">
         <v>45935</v>
       </c>
-      <c r="O66" s="45">
-        <v>46192.964436180555</v>
-      </c>
-      <c r="P66" s="45">
-        <v>46192.964436180555</v>
-      </c>
+      <c r="O66" s="45"/>
+      <c r="P66" s="45"/>
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
@@ -7296,19 +7336,19 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>305</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="D67" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="B67" s="49" t="s">
+      <c r="E67" s="49" t="s">
         <v>308</v>
-      </c>
-      <c r="C67" s="49" t="s">
-        <v>309</v>
-      </c>
-      <c r="D67" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="E67" s="49" t="s">
-        <v>311</v>
       </c>
       <c r="F67" s="50"/>
       <c r="G67" s="50" t="s">
@@ -7316,34 +7356,34 @@
       </c>
       <c r="H67" s="50"/>
       <c r="I67" s="45" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J67" s="51"/>
       <c r="K67" s="47"/>
       <c r="L67" s="50"/>
       <c r="N67" s="51"/>
-      <c r="O67" s="45">
-        <v>46192.964436180555</v>
-      </c>
-      <c r="P67" s="45">
-        <v>46192.964436180555</v>
+      <c r="O67" s="53">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P67" s="53">
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="48" t="s">
+        <v>310</v>
+      </c>
+      <c r="B68" s="49" t="s">
+        <v>311</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="D68" s="49" t="s">
         <v>313</v>
       </c>
-      <c r="B68" s="49" t="s">
+      <c r="E68" s="49" t="s">
         <v>314</v>
-      </c>
-      <c r="C68" s="49" t="s">
-        <v>315</v>
-      </c>
-      <c r="D68" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="E68" s="49" t="s">
-        <v>317</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>51</v>
@@ -7355,7 +7395,7 @@
         <v>38</v>
       </c>
       <c r="I68" s="45" t="s">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="J68" s="51">
         <v>45877</v>
@@ -7371,10 +7411,10 @@
         <v>45935</v>
       </c>
       <c r="O68" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P68" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
@@ -7389,19 +7429,19 @@
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="48" t="s">
+        <v>315</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="D69" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="E69" s="49" t="s">
         <v>319</v>
-      </c>
-      <c r="B69" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="C69" s="49" t="s">
-        <v>321</v>
-      </c>
-      <c r="D69" s="49" t="s">
-        <v>322</v>
-      </c>
-      <c r="E69" s="49" t="s">
-        <v>323</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>51</v>
@@ -7413,7 +7453,7 @@
         <v>38</v>
       </c>
       <c r="I69" s="45" t="s">
-        <v>324</v>
+        <v>167</v>
       </c>
       <c r="J69" s="51">
         <v>45877</v>
@@ -7429,10 +7469,10 @@
         <v>45935</v>
       </c>
       <c r="O69" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P69" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q69" s="4"/>
       <c r="R69" s="4"/>
@@ -7447,31 +7487,31 @@
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="48" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B70" s="49" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E70" s="49" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G70" s="50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H70" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I70" s="45" t="s">
-        <v>329</v>
+        <v>108</v>
       </c>
       <c r="J70" s="51">
         <v>45877</v>
@@ -7487,10 +7527,10 @@
         <v>45935</v>
       </c>
       <c r="O70" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P70" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
@@ -7505,31 +7545,31 @@
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="48" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B71" s="49" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E71" s="49" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G71" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H71" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I71" s="45" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J71" s="51">
         <v>45877</v>
@@ -7544,8 +7584,12 @@
       <c r="N71" s="51">
         <v>45935</v>
       </c>
-      <c r="O71" s="45"/>
-      <c r="P71" s="45"/>
+      <c r="O71" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P71" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
@@ -7559,31 +7603,31 @@
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B72" s="49" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E72" s="49" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G72" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H72" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I72" s="45" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J72" s="51">
         <v>45877</v>
@@ -7598,8 +7642,12 @@
       <c r="N72" s="51">
         <v>45935</v>
       </c>
-      <c r="O72" s="45"/>
-      <c r="P72" s="45"/>
+      <c r="O72" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P72" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
@@ -7613,31 +7661,31 @@
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="48" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B73" s="49" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C73" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="D73" s="49" t="s">
+        <v>336</v>
+      </c>
+      <c r="E73" s="49" t="s">
         <v>337</v>
-      </c>
-      <c r="D73" s="49" t="s">
-        <v>342</v>
-      </c>
-      <c r="E73" s="49" t="s">
-        <v>343</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H73" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I73" s="45" t="s">
-        <v>344</v>
+        <v>167</v>
       </c>
       <c r="J73" s="51">
         <v>45877</v>
@@ -7652,8 +7700,12 @@
       <c r="N73" s="51">
         <v>45935</v>
       </c>
-      <c r="O73" s="45"/>
-      <c r="P73" s="45"/>
+      <c r="O73" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P73" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q73" s="4"/>
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
@@ -7667,31 +7719,31 @@
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="48" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B74" s="49" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>192</v>
       </c>
       <c r="E74" s="49" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G74" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H74" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I74" s="45" t="s">
-        <v>349</v>
+        <v>167</v>
       </c>
       <c r="J74" s="51">
         <v>45877</v>
@@ -7706,8 +7758,12 @@
       <c r="N74" s="51">
         <v>45935</v>
       </c>
-      <c r="O74" s="45"/>
-      <c r="P74" s="45"/>
+      <c r="O74" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P74" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
@@ -7721,19 +7777,19 @@
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="48" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B75" s="49" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C75" s="49" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D75" s="49" t="s">
         <v>198</v>
       </c>
       <c r="E75" s="49" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>51</v>
@@ -7745,7 +7801,7 @@
         <v>38</v>
       </c>
       <c r="I75" s="45" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="J75" s="51">
         <v>45877</v>
@@ -7775,19 +7831,19 @@
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="48" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B76" s="49" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C76" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="D76" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="E76" s="49" t="s">
         <v>348</v>
-      </c>
-      <c r="D76" s="49" t="s">
-        <v>355</v>
-      </c>
-      <c r="E76" s="49" t="s">
-        <v>356</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>51</v>
@@ -7799,7 +7855,7 @@
         <v>38</v>
       </c>
       <c r="I76" s="45" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J76" s="51">
         <v>45877</v>
@@ -7829,19 +7885,19 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="48" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E77" s="49" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F77" s="50"/>
       <c r="G77" s="50" t="s">
@@ -7849,22 +7905,22 @@
       </c>
       <c r="H77" s="50"/>
       <c r="I77" s="45" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="J77" s="51"/>
       <c r="K77" s="47"/>
       <c r="L77" s="50"/>
       <c r="N77" s="51"/>
       <c r="O77" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P77" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="54" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B78" s="54"/>
       <c r="C78" s="54"/>
@@ -7902,19 +7958,19 @@
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="48" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B79" s="49" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E79" s="49" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>51</v>
@@ -7926,7 +7982,7 @@
         <v>38</v>
       </c>
       <c r="I79" s="45" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="J79" s="51">
         <v>45877</v>
@@ -7942,10 +7998,10 @@
         <v>45935</v>
       </c>
       <c r="O79" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P79" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
@@ -7960,19 +8016,19 @@
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="48" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B80" s="49" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C80" s="49" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E80" s="49" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>51</v>
@@ -7984,7 +8040,7 @@
         <v>38</v>
       </c>
       <c r="I80" s="45" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="J80" s="51">
         <v>45877</v>
@@ -8014,19 +8070,19 @@
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="48" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B81" s="49" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E81" s="49" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>51</v>
@@ -8038,7 +8094,7 @@
         <v>38</v>
       </c>
       <c r="I81" s="45" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="J81" s="51">
         <v>45877</v>
@@ -8054,10 +8110,10 @@
         <v>45935</v>
       </c>
       <c r="O81" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P81" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
@@ -8072,19 +8128,19 @@
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="48" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B82" s="49" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C82" s="49" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E82" s="49" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>51</v>
@@ -8096,7 +8152,7 @@
         <v>38</v>
       </c>
       <c r="I82" s="45" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="J82" s="51">
         <v>45877</v>
@@ -8112,10 +8168,10 @@
         <v>45935</v>
       </c>
       <c r="O82" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P82" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q82" s="4"/>
       <c r="R82" s="4"/>
@@ -8130,19 +8186,19 @@
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="48" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B83" s="49" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C83" s="49" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D83" s="49" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E83" s="49" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>51</v>
@@ -8154,7 +8210,7 @@
         <v>38</v>
       </c>
       <c r="I83" s="45" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="J83" s="51">
         <v>45877</v>
@@ -8170,10 +8226,10 @@
         <v>45935</v>
       </c>
       <c r="O83" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P83" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
@@ -8188,19 +8244,19 @@
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="48" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B84" s="49" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C84" s="49" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D84" s="49" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E84" s="49" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>51</v>
@@ -8212,7 +8268,7 @@
         <v>38</v>
       </c>
       <c r="I84" s="45" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="J84" s="51">
         <v>45877</v>
@@ -8228,10 +8284,10 @@
         <v>45935</v>
       </c>
       <c r="O84" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P84" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q84" s="4"/>
       <c r="R84" s="4"/>
@@ -8246,19 +8302,19 @@
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="48" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B85" s="49" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E85" s="49" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>51</v>
@@ -8270,7 +8326,7 @@
         <v>38</v>
       </c>
       <c r="I85" s="45" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="J85" s="51">
         <v>45877</v>
@@ -8286,10 +8342,10 @@
         <v>45935</v>
       </c>
       <c r="O85" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P85" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
@@ -8304,19 +8360,19 @@
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="48" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B86" s="49" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C86" s="49" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E86" s="49" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>51</v>
@@ -8328,7 +8384,7 @@
         <v>38</v>
       </c>
       <c r="I86" s="45" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="J86" s="51">
         <v>45877</v>
@@ -8344,10 +8400,10 @@
         <v>45935</v>
       </c>
       <c r="O86" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P86" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q86" s="4"/>
       <c r="R86" s="4"/>
@@ -8362,19 +8418,19 @@
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B87" s="49" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E87" s="49" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>51</v>
@@ -8386,7 +8442,7 @@
         <v>38</v>
       </c>
       <c r="I87" s="45" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J87" s="51">
         <v>45877</v>
@@ -8402,10 +8458,10 @@
         <v>45935</v>
       </c>
       <c r="O87" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P87" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
@@ -8420,19 +8476,19 @@
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="48" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B88" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E88" s="49" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>51</v>
@@ -8444,7 +8500,7 @@
         <v>38</v>
       </c>
       <c r="I88" s="45" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="J88" s="51">
         <v>45877</v>
@@ -8460,10 +8516,10 @@
         <v>45935</v>
       </c>
       <c r="O88" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P88" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q88" s="4"/>
       <c r="R88" s="4"/>
@@ -8478,19 +8534,19 @@
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="48" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B89" s="49" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C89" s="49" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E89" s="49" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>51</v>
@@ -8502,7 +8558,7 @@
         <v>38</v>
       </c>
       <c r="I89" s="45" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="J89" s="51">
         <v>45877</v>
@@ -8518,10 +8574,10 @@
         <v>45935</v>
       </c>
       <c r="O89" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P89" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
@@ -8536,19 +8592,19 @@
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="48" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B90" s="49" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E90" s="49" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>51</v>
@@ -8560,7 +8616,7 @@
         <v>38</v>
       </c>
       <c r="I90" s="45" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="J90" s="51">
         <v>45877</v>
@@ -8576,10 +8632,10 @@
         <v>45935</v>
       </c>
       <c r="O90" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P90" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q90" s="4"/>
       <c r="R90" s="4"/>
@@ -8594,19 +8650,19 @@
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="48" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B91" s="49" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C91" s="49" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E91" s="49" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>51</v>
@@ -8618,7 +8674,7 @@
         <v>38</v>
       </c>
       <c r="I91" s="45" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="J91" s="51">
         <v>45877</v>
@@ -8634,10 +8690,10 @@
         <v>45935</v>
       </c>
       <c r="O91" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P91" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
@@ -8652,31 +8708,31 @@
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="48" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B92" s="49" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C92" s="49" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E92" s="49" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G92" s="50" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H92" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I92" s="45" t="s">
-        <v>108</v>
+        <v>438</v>
       </c>
       <c r="J92" s="51">
         <v>45877</v>
@@ -8691,8 +8747,12 @@
       <c r="N92" s="51">
         <v>45935</v>
       </c>
-      <c r="O92" s="45"/>
-      <c r="P92" s="45"/>
+      <c r="O92" s="45">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P92" s="45">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q92" s="4"/>
       <c r="R92" s="4"/>
       <c r="S92" s="4"/>
@@ -8706,7 +8766,7 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="42" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B93" s="42"/>
       <c r="C93" s="42"/>
@@ -8738,19 +8798,19 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="57" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B94" s="49" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C94" s="49" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E94" s="49" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>51</v>
@@ -8762,7 +8822,7 @@
         <v>38</v>
       </c>
       <c r="I94" s="45" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="J94" s="51">
         <v>45877</v>
@@ -8778,10 +8838,10 @@
         <v>45935</v>
       </c>
       <c r="O94" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P94" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
@@ -8796,19 +8856,19 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="57" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B95" s="49" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C95" s="49" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E95" s="49" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>51</v>
@@ -8820,7 +8880,7 @@
         <v>38</v>
       </c>
       <c r="I95" s="45" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="J95" s="51">
         <v>45877</v>
@@ -8836,10 +8896,10 @@
         <v>45935</v>
       </c>
       <c r="O95" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P95" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
@@ -8854,19 +8914,19 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="57" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B96" s="49" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C96" s="49" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E96" s="49" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>51</v>
@@ -8878,7 +8938,7 @@
         <v>38</v>
       </c>
       <c r="I96" s="45" t="s">
-        <v>463</v>
+        <v>108</v>
       </c>
       <c r="J96" s="51">
         <v>45877</v>
@@ -8894,10 +8954,10 @@
         <v>45935</v>
       </c>
       <c r="O96" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P96" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q96" s="4"/>
       <c r="R96" s="4"/>
@@ -8912,19 +8972,19 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="57" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B97" s="49" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C97" s="49" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E97" s="49" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>51</v>
@@ -8936,7 +8996,7 @@
         <v>38</v>
       </c>
       <c r="I97" s="45" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="J97" s="51">
         <v>45877</v>
@@ -8952,10 +9012,10 @@
         <v>45935</v>
       </c>
       <c r="O97" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P97" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
@@ -8970,19 +9030,19 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="57" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B98" s="49" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C98" s="49" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="E98" s="49" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F98" s="50" t="s">
         <v>51</v>
@@ -8994,7 +9054,7 @@
         <v>38</v>
       </c>
       <c r="I98" s="45" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="J98" s="51">
         <v>45877</v>
@@ -9010,10 +9070,10 @@
         <v>45935</v>
       </c>
       <c r="O98" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P98" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
@@ -9028,19 +9088,19 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="57" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B99" s="49" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C99" s="49" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E99" s="49" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>51</v>
@@ -9052,7 +9112,7 @@
         <v>38</v>
       </c>
       <c r="I99" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J99" s="51">
         <v>45877</v>
@@ -9082,19 +9142,19 @@
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="57" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B100" s="49" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C100" s="49" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="E100" s="49" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>51</v>
@@ -9106,7 +9166,7 @@
         <v>38</v>
       </c>
       <c r="I100" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J100" s="51">
         <v>45877</v>
@@ -9136,19 +9196,19 @@
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="57" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="B101" s="49" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E101" s="49" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>51</v>
@@ -9160,7 +9220,7 @@
         <v>38</v>
       </c>
       <c r="I101" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J101" s="51">
         <v>45877</v>
@@ -9190,19 +9250,19 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="57" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B102" s="49" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C102" s="49" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E102" s="49" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>51</v>
@@ -9214,7 +9274,7 @@
         <v>38</v>
       </c>
       <c r="I102" s="45" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="J102" s="51">
         <v>45877</v>
@@ -9230,10 +9290,10 @@
         <v>45935</v>
       </c>
       <c r="O102" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P102" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
@@ -9248,19 +9308,19 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="57" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B103" s="49" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="E103" s="49" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>51</v>
@@ -9272,7 +9332,7 @@
         <v>38</v>
       </c>
       <c r="I103" s="45" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="J103" s="51">
         <v>45877</v>
@@ -9302,31 +9362,31 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="57" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B104" s="49" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C104" s="49" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="E104" s="49" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G104" s="50" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H104" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I104" s="45" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="J104" s="51">
         <v>45877</v>
@@ -9342,10 +9402,10 @@
         <v>45935</v>
       </c>
       <c r="O104" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P104" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
@@ -9360,19 +9420,19 @@
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="57" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B105" s="49" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C105" s="49" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E105" s="49" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="F105" s="50" t="s">
         <v>51</v>
@@ -9384,7 +9444,7 @@
         <v>38</v>
       </c>
       <c r="I105" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J105" s="51">
         <v>45877</v>
@@ -9414,19 +9474,19 @@
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="57" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B106" s="49" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C106" s="49" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E106" s="49" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F106" s="50" t="s">
         <v>51</v>
@@ -9438,7 +9498,7 @@
         <v>38</v>
       </c>
       <c r="I106" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J106" s="51">
         <v>45877</v>
@@ -9468,19 +9528,19 @@
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="57" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B107" s="49" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C107" s="49" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E107" s="49" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F107" s="50" t="s">
         <v>51</v>
@@ -9492,7 +9552,7 @@
         <v>38</v>
       </c>
       <c r="I107" s="45" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J107" s="51">
         <v>45877</v>
@@ -9522,19 +9582,19 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="57" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B108" s="49" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C108" s="49" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E108" s="49" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="F108" s="50" t="s">
         <v>51</v>
@@ -9546,7 +9606,7 @@
         <v>38</v>
       </c>
       <c r="I108" s="45" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="J108" s="51">
         <v>45877</v>
@@ -9562,10 +9622,10 @@
         <v>45935</v>
       </c>
       <c r="O108" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P108" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="Q108" s="4"/>
       <c r="R108" s="4"/>
@@ -9580,19 +9640,19 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="57" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B109" s="49" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C109" s="49" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D109" s="49" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E109" s="49" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F109" s="50"/>
       <c r="G109" s="50" t="s">
@@ -9600,17 +9660,17 @@
       </c>
       <c r="H109" s="50"/>
       <c r="I109" s="45" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="J109" s="51"/>
       <c r="K109" s="47"/>
       <c r="L109" s="50"/>
       <c r="N109" s="51"/>
       <c r="O109" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P109" s="45">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.25">
@@ -9671,7 +9731,7 @@
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="54" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B112" s="54"/>
       <c r="C112" s="54"/>
@@ -9709,19 +9769,19 @@
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="48" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B113" s="49" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C113" s="49" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E113" s="49" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="F113" s="50" t="s">
         <v>51</v>
@@ -9733,7 +9793,7 @@
         <v>38</v>
       </c>
       <c r="I113" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J113" s="51">
         <v>45877</v>
@@ -9763,19 +9823,19 @@
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="48" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B114" s="49" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C114" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E114" s="49" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="F114" s="50" t="s">
         <v>51</v>
@@ -9787,7 +9847,7 @@
         <v>38</v>
       </c>
       <c r="I114" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J114" s="51">
         <v>45877</v>
@@ -9817,19 +9877,19 @@
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B115" s="49" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C115" s="49" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E115" s="49" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="F115" s="50" t="s">
         <v>51</v>
@@ -9841,7 +9901,7 @@
         <v>38</v>
       </c>
       <c r="I115" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J115" s="51">
         <v>45877</v>
@@ -9871,19 +9931,19 @@
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="48" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B116" s="49" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C116" s="49" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="E116" s="49" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="F116" s="50" t="s">
         <v>51</v>
@@ -9895,7 +9955,7 @@
         <v>38</v>
       </c>
       <c r="I116" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J116" s="51">
         <v>45877</v>
@@ -9925,19 +9985,19 @@
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="48" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B117" s="49" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C117" s="49" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E117" s="49" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="F117" s="50" t="s">
         <v>51</v>
@@ -9949,7 +10009,7 @@
         <v>38</v>
       </c>
       <c r="I117" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J117" s="51">
         <v>45877</v>
@@ -9979,19 +10039,19 @@
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="48" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B118" s="49" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C118" s="49" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E118" s="49" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="F118" s="50" t="s">
         <v>51</v>
@@ -10003,7 +10063,7 @@
         <v>38</v>
       </c>
       <c r="I118" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J118" s="51">
         <v>45877</v>
@@ -10033,19 +10093,19 @@
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="48" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B119" s="49" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C119" s="49" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E119" s="49" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="F119" s="50" t="s">
         <v>51</v>
@@ -10057,7 +10117,7 @@
         <v>38</v>
       </c>
       <c r="I119" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J119" s="51">
         <v>45877</v>
@@ -10087,19 +10147,19 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="48" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B120" s="49" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C120" s="49" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E120" s="49" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="F120" s="50"/>
       <c r="G120" s="50" t="s">
@@ -10107,34 +10167,34 @@
       </c>
       <c r="H120" s="50"/>
       <c r="I120" s="45" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="J120" s="51"/>
       <c r="K120" s="47"/>
       <c r="L120" s="50"/>
       <c r="N120" s="51"/>
       <c r="O120" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P120" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="48" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B121" s="49" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C121" s="49" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="E121" s="49" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="F121" s="50" t="s">
         <v>51</v>
@@ -10146,7 +10206,7 @@
         <v>38</v>
       </c>
       <c r="I121" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J121" s="51">
         <v>45877</v>
@@ -10176,19 +10236,19 @@
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="48" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B122" s="49" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E122" s="49" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="F122" s="50" t="s">
         <v>51</v>
@@ -10200,7 +10260,7 @@
         <v>38</v>
       </c>
       <c r="I122" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J122" s="51">
         <v>45877</v>
@@ -10230,19 +10290,19 @@
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="48" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B123" s="49" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C123" s="49" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="E123" s="49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F123" s="50" t="s">
         <v>51</v>
@@ -10254,7 +10314,7 @@
         <v>38</v>
       </c>
       <c r="I123" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J123" s="51">
         <v>45877</v>
@@ -10284,19 +10344,19 @@
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="48" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B124" s="49" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E124" s="49" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="F124" s="50" t="s">
         <v>51</v>
@@ -10308,7 +10368,7 @@
         <v>38</v>
       </c>
       <c r="I124" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J124" s="51">
         <v>45877</v>
@@ -10338,19 +10398,19 @@
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="48" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B125" s="49" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C125" s="49" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="E125" s="49" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F125" s="50" t="s">
         <v>51</v>
@@ -10362,7 +10422,7 @@
         <v>38</v>
       </c>
       <c r="I125" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J125" s="51">
         <v>45877</v>
@@ -10392,19 +10452,19 @@
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="48" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B126" s="49" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C126" s="49" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="E126" s="49" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="F126" s="50" t="s">
         <v>51</v>
@@ -10416,7 +10476,7 @@
         <v>38</v>
       </c>
       <c r="I126" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J126" s="51">
         <v>45877</v>
@@ -10446,19 +10506,19 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="48" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B127" s="49" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C127" s="49" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="E127" s="49" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="F127" s="50"/>
       <c r="G127" s="50" t="s">
@@ -10466,34 +10526,34 @@
       </c>
       <c r="H127" s="50"/>
       <c r="I127" s="45" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="J127" s="51"/>
       <c r="K127" s="47"/>
       <c r="L127" s="50"/>
       <c r="N127" s="51"/>
       <c r="O127" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P127" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="48" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B128" s="49" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C128" s="49" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="E128" s="49" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="F128" s="50" t="s">
         <v>51</v>
@@ -10505,7 +10565,7 @@
         <v>38</v>
       </c>
       <c r="I128" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J128" s="51">
         <v>45877</v>
@@ -10535,19 +10595,19 @@
     </row>
     <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="48" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B129" s="49" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C129" s="49" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E129" s="49" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="F129" s="50" t="s">
         <v>51</v>
@@ -10559,7 +10619,7 @@
         <v>38</v>
       </c>
       <c r="I129" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J129" s="51">
         <v>45877</v>
@@ -10589,19 +10649,19 @@
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="48" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B130" s="49" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C130" s="49" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="D130" s="49" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="E130" s="49" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="F130" s="50" t="s">
         <v>51</v>
@@ -10613,7 +10673,7 @@
         <v>38</v>
       </c>
       <c r="I130" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J130" s="51">
         <v>45877</v>
@@ -10643,19 +10703,19 @@
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="48" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B131" s="49" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="C131" s="49" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E131" s="49" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F131" s="50" t="s">
         <v>51</v>
@@ -10667,7 +10727,7 @@
         <v>51</v>
       </c>
       <c r="I131" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J131" s="51">
         <v>45877</v>
@@ -10697,19 +10757,19 @@
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="48" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B132" s="49" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C132" s="49" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E132" s="49" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F132" s="50" t="s">
         <v>51</v>
@@ -10721,7 +10781,7 @@
         <v>38</v>
       </c>
       <c r="I132" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J132" s="51">
         <v>45877</v>
@@ -10751,19 +10811,19 @@
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="48" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B133" s="49" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C133" s="49" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E133" s="49" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F133" s="50" t="s">
         <v>51</v>
@@ -10775,7 +10835,7 @@
         <v>38</v>
       </c>
       <c r="I133" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J133" s="51">
         <v>45877</v>
@@ -10805,19 +10865,19 @@
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="48" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B134" s="49" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C134" s="49" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E134" s="49" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="F134" s="50" t="s">
         <v>51</v>
@@ -10829,7 +10889,7 @@
         <v>38</v>
       </c>
       <c r="I134" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J134" s="51">
         <v>45877</v>
@@ -10859,19 +10919,19 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="48" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B135" s="49" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C135" s="49" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E135" s="49" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F135" s="50"/>
       <c r="G135" s="50" t="s">
@@ -10879,22 +10939,22 @@
       </c>
       <c r="H135" s="50"/>
       <c r="I135" s="45" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="J135" s="51"/>
       <c r="K135" s="47"/>
       <c r="L135" s="50"/>
       <c r="N135" s="51"/>
       <c r="O135" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P135" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="42" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B136" s="42"/>
       <c r="C136" s="42"/>
@@ -10930,19 +10990,19 @@
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="48" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B137" s="49" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="C137" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="E137" s="49" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="F137" s="50" t="s">
         <v>51</v>
@@ -10954,7 +11014,7 @@
         <v>38</v>
       </c>
       <c r="I137" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J137" s="51">
         <v>45877</v>
@@ -10984,19 +11044,19 @@
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="B138" s="49" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C138" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="E138" s="49" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F138" s="50" t="s">
         <v>51</v>
@@ -11008,7 +11068,7 @@
         <v>38</v>
       </c>
       <c r="I138" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J138" s="51">
         <v>45877</v>
@@ -11038,19 +11098,19 @@
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="48" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B139" s="49" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C139" s="49" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="E139" s="49" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F139" s="50" t="s">
         <v>51</v>
@@ -11062,7 +11122,7 @@
         <v>38</v>
       </c>
       <c r="I139" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J139" s="51">
         <v>45877</v>
@@ -11092,19 +11152,19 @@
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="48" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="B140" s="49" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C140" s="49" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="D140" s="49" t="s">
         <v>192</v>
       </c>
       <c r="E140" s="49" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="F140" s="50" t="s">
         <v>51</v>
@@ -11116,7 +11176,7 @@
         <v>38</v>
       </c>
       <c r="I140" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J140" s="51">
         <v>45877</v>
@@ -11146,19 +11206,19 @@
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="48" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B141" s="49" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C141" s="49" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E141" s="49" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="F141" s="50" t="s">
         <v>51</v>
@@ -11170,7 +11230,7 @@
         <v>38</v>
       </c>
       <c r="I141" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J141" s="51">
         <v>45877</v>
@@ -11200,19 +11260,19 @@
     </row>
     <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="48" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B142" s="49" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C142" s="49" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="E142" s="49" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="F142" s="50" t="s">
         <v>51</v>
@@ -11224,7 +11284,7 @@
         <v>38</v>
       </c>
       <c r="I142" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J142" s="51">
         <v>45877</v>
@@ -11254,19 +11314,19 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="48" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B143" s="49" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="C143" s="49" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E143" s="49" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F143" s="50"/>
       <c r="G143" s="50" t="s">
@@ -11274,34 +11334,34 @@
       </c>
       <c r="H143" s="50"/>
       <c r="I143" s="45" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="J143" s="51"/>
       <c r="K143" s="47"/>
       <c r="L143" s="50"/>
       <c r="N143" s="51"/>
       <c r="O143" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P143" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B144" s="49" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="D144" s="49" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="E144" s="49" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="F144" s="50" t="s">
         <v>51</v>
@@ -11313,7 +11373,7 @@
         <v>38</v>
       </c>
       <c r="I144" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J144" s="51">
         <v>45877</v>
@@ -11343,19 +11403,19 @@
     </row>
     <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="48" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B145" s="49" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C145" s="49" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="E145" s="49" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="F145" s="50" t="s">
         <v>51</v>
@@ -11367,7 +11427,7 @@
         <v>38</v>
       </c>
       <c r="I145" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J145" s="51">
         <v>45877</v>
@@ -11397,19 +11457,19 @@
     </row>
     <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="48" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B146" s="49" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C146" s="49" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="E146" s="49" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="F146" s="50" t="s">
         <v>51</v>
@@ -11421,7 +11481,7 @@
         <v>38</v>
       </c>
       <c r="I146" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J146" s="51">
         <v>45877</v>
@@ -11451,19 +11511,19 @@
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="48" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B147" s="49" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C147" s="49" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="D147" s="49" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E147" s="49" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="F147" s="50" t="s">
         <v>51</v>
@@ -11475,7 +11535,7 @@
         <v>38</v>
       </c>
       <c r="I147" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J147" s="51">
         <v>45877</v>
@@ -11505,19 +11565,19 @@
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="48" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B148" s="49" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C148" s="49" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E148" s="49" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="F148" s="50" t="s">
         <v>51</v>
@@ -11529,7 +11589,7 @@
         <v>38</v>
       </c>
       <c r="I148" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J148" s="51">
         <v>45877</v>
@@ -11559,19 +11619,19 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="48" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B149" s="49" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C149" s="49" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="E149" s="49" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="F149" s="50"/>
       <c r="G149" s="50" t="s">
@@ -11579,22 +11639,22 @@
       </c>
       <c r="H149" s="50"/>
       <c r="I149" s="45" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="J149" s="51"/>
       <c r="K149" s="47"/>
       <c r="L149" s="50"/>
       <c r="N149" s="51"/>
       <c r="O149" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P149" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="42" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B150" s="42"/>
       <c r="C150" s="42"/>
@@ -11624,19 +11684,19 @@
     </row>
     <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="48" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="B151" s="49" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="C151" s="49" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="E151" s="49" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="F151" s="50" t="s">
         <v>51</v>
@@ -11648,7 +11708,7 @@
         <v>38</v>
       </c>
       <c r="I151" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J151" s="51">
         <v>45877</v>
@@ -11678,19 +11738,19 @@
     </row>
     <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="48" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="B152" s="49" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="C152" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="E152" s="49" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F152" s="50" t="s">
         <v>51</v>
@@ -11702,7 +11762,7 @@
         <v>38</v>
       </c>
       <c r="I152" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J152" s="51">
         <v>45877</v>
@@ -11732,19 +11792,19 @@
     </row>
     <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="48" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="B153" s="49" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="C153" s="49" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D153" s="49" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="E153" s="49" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F153" s="50" t="s">
         <v>51</v>
@@ -11756,7 +11816,7 @@
         <v>38</v>
       </c>
       <c r="I153" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J153" s="51">
         <v>45877</v>
@@ -11786,19 +11846,19 @@
     </row>
     <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="48" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B154" s="49" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C154" s="49" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="D154" s="49" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="E154" s="49" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F154" s="50" t="s">
         <v>51</v>
@@ -11810,7 +11870,7 @@
         <v>38</v>
       </c>
       <c r="I154" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J154" s="51">
         <v>45878</v>
@@ -11840,19 +11900,19 @@
     </row>
     <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="48" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="B155" s="49" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="C155" s="49" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E155" s="49" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F155" s="50" t="s">
         <v>51</v>
@@ -11864,7 +11924,7 @@
         <v>38</v>
       </c>
       <c r="I155" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J155" s="51">
         <v>45879</v>
@@ -11894,19 +11954,19 @@
     </row>
     <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B156" s="49" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C156" s="49" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="E156" s="49" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="F156" s="50" t="s">
         <v>51</v>
@@ -11918,7 +11978,7 @@
         <v>38</v>
       </c>
       <c r="I156" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J156" s="51">
         <v>45880</v>
@@ -11948,19 +12008,19 @@
     </row>
     <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="48" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="B157" s="49" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C157" s="49" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D157" s="49" t="s">
         <v>198</v>
       </c>
       <c r="E157" s="49" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="F157" s="50" t="s">
         <v>51</v>
@@ -11972,7 +12032,7 @@
         <v>38</v>
       </c>
       <c r="I157" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J157" s="51">
         <v>45881</v>
@@ -12002,19 +12062,19 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="48" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="B158" s="49" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="C158" s="49" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="D158" s="49" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="E158" s="49" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="F158" s="50"/>
       <c r="G158" s="50" t="s">
@@ -12022,34 +12082,34 @@
       </c>
       <c r="H158" s="50"/>
       <c r="I158" s="45" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="J158" s="51"/>
       <c r="K158" s="47"/>
       <c r="L158" s="50"/>
       <c r="N158" s="51"/>
       <c r="O158" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P158" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="48" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B159" s="49" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C159" s="49" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="E159" s="49" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="F159" s="50" t="s">
         <v>51</v>
@@ -12061,7 +12121,7 @@
         <v>38</v>
       </c>
       <c r="I159" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J159" s="51">
         <v>45881</v>
@@ -12091,19 +12151,19 @@
     </row>
     <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="48" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B160" s="49" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="C160" s="49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D160" s="49" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="E160" s="49" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="F160" s="50" t="s">
         <v>51</v>
@@ -12115,7 +12175,7 @@
         <v>38</v>
       </c>
       <c r="I160" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J160" s="51">
         <v>45881</v>
@@ -12145,19 +12205,19 @@
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="48" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="B161" s="49" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="C161" s="49" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="D161" s="49" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="E161" s="49" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F161" s="50" t="s">
         <v>51</v>
@@ -12169,7 +12229,7 @@
         <v>38</v>
       </c>
       <c r="I161" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J161" s="51">
         <v>45881</v>
@@ -12199,19 +12259,19 @@
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="B162" s="49" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C162" s="49" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="D162" s="49" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E162" s="49" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F162" s="50" t="s">
         <v>51</v>
@@ -12223,7 +12283,7 @@
         <v>38</v>
       </c>
       <c r="I162" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J162" s="51">
         <v>45881</v>
@@ -12253,19 +12313,19 @@
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="48" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="B163" s="49" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="C163" s="49" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="D163" s="49" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="E163" s="49" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="F163" s="50" t="s">
         <v>51</v>
@@ -12277,7 +12337,7 @@
         <v>38</v>
       </c>
       <c r="I163" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J163" s="51">
         <v>45881</v>
@@ -12307,19 +12367,19 @@
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="48" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="B164" s="49" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="C164" s="49" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D164" s="49" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="E164" s="49" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="F164" s="50" t="s">
         <v>51</v>
@@ -12331,7 +12391,7 @@
         <v>38</v>
       </c>
       <c r="I164" s="45" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J164" s="51">
         <v>45881</v>
@@ -12361,19 +12421,19 @@
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="48" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="B165" s="49" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C165" s="49" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D165" s="49" t="s">
         <v>198</v>
       </c>
       <c r="E165" s="49" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="F165" s="50" t="s">
         <v>51</v>
@@ -12385,7 +12445,7 @@
         <v>38</v>
       </c>
       <c r="I165" s="45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J165" s="51">
         <v>45881</v>
@@ -12415,19 +12475,19 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="48" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="B166" s="49" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="C166" s="49" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="E166" s="49" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="F166" s="50"/>
       <c r="G166" s="50" t="s">
@@ -12435,22 +12495,22 @@
       </c>
       <c r="H166" s="50"/>
       <c r="I166" s="45" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="J166" s="51"/>
       <c r="K166" s="47"/>
       <c r="L166" s="50"/>
       <c r="N166" s="51"/>
       <c r="O166" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P166" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="42" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="B167" s="42"/>
       <c r="C167" s="42"/>
@@ -12486,19 +12546,19 @@
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="48" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="B168" s="49" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="C168" s="49" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="D168" s="49" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="E168" s="49" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="F168" s="50" t="s">
         <v>51</v>
@@ -12510,7 +12570,7 @@
         <v>38</v>
       </c>
       <c r="I168" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J168" s="51">
         <v>45881</v>
@@ -12540,19 +12600,19 @@
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="48" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="B169" s="49" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="C169" s="49" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="D169" s="49" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="E169" s="49" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="F169" s="50" t="s">
         <v>51</v>
@@ -12564,7 +12624,7 @@
         <v>38</v>
       </c>
       <c r="I169" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J169" s="51">
         <v>45881</v>
@@ -12594,19 +12654,19 @@
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="48" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="B170" s="49" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="C170" s="49" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="D170" s="49" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E170" s="49" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="F170" s="50" t="s">
         <v>51</v>
@@ -12618,7 +12678,7 @@
         <v>38</v>
       </c>
       <c r="I170" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J170" s="51">
         <v>45881</v>
@@ -12648,19 +12708,19 @@
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="48" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="B171" s="49" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="C171" s="49" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="D171" s="49" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="E171" s="49" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="F171" s="50" t="s">
         <v>51</v>
@@ -12672,7 +12732,7 @@
         <v>38</v>
       </c>
       <c r="I171" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J171" s="51">
         <v>45881</v>
@@ -12702,19 +12762,19 @@
     </row>
     <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="48" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="B172" s="49" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C172" s="49" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="D172" s="49" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E172" s="49" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="F172" s="50" t="s">
         <v>51</v>
@@ -12726,7 +12786,7 @@
         <v>38</v>
       </c>
       <c r="I172" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J172" s="51">
         <v>45881</v>
@@ -12756,19 +12816,19 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="48" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="B173" s="49" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="C173" s="49" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="E173" s="49" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="F173" s="50" t="s">
         <v>51</v>
@@ -12780,7 +12840,7 @@
         <v>38</v>
       </c>
       <c r="I173" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J173" s="51">
         <v>45881</v>
@@ -12810,19 +12870,19 @@
     </row>
     <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="48" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="B174" s="49" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C174" s="49" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="D174" s="49" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E174" s="49" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="F174" s="50" t="s">
         <v>51</v>
@@ -12834,7 +12894,7 @@
         <v>38</v>
       </c>
       <c r="I174" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J174" s="51">
         <v>45881</v>
@@ -12864,19 +12924,19 @@
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="48" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="B175" s="49" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C175" s="49" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D175" s="49" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="E175" s="49" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="F175" s="50" t="s">
         <v>51</v>
@@ -12888,7 +12948,7 @@
         <v>38</v>
       </c>
       <c r="I175" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J175" s="51">
         <v>45881</v>
@@ -12918,19 +12978,19 @@
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="48" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="B176" s="49" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="C176" s="49" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="D176" s="49" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="E176" s="49" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="F176" s="50" t="s">
         <v>51</v>
@@ -12942,7 +13002,7 @@
         <v>38</v>
       </c>
       <c r="I176" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J176" s="51">
         <v>45881</v>
@@ -12972,19 +13032,19 @@
     </row>
     <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="48" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="B177" s="49" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="C177" s="49" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E177" s="49" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="F177" s="50" t="s">
         <v>51</v>
@@ -12996,7 +13056,7 @@
         <v>38</v>
       </c>
       <c r="I177" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J177" s="51">
         <v>45881</v>
@@ -13026,19 +13086,19 @@
     </row>
     <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="48" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="B178" s="59" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="C178" s="59" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D178" s="59" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="E178" s="59" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="F178" s="50" t="s">
         <v>51</v>
@@ -13050,7 +13110,7 @@
         <v>38</v>
       </c>
       <c r="I178" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J178" s="51">
         <v>45881</v>
@@ -13080,19 +13140,19 @@
     </row>
     <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="48" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B179" s="59" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="C179" s="59" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D179" s="59" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="E179" s="59" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="F179" s="50" t="s">
         <v>51</v>
@@ -13104,7 +13164,7 @@
         <v>38</v>
       </c>
       <c r="I179" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J179" s="51">
         <v>45881</v>
@@ -13134,19 +13194,19 @@
     </row>
     <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="48" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="B180" s="49" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="C180" s="49" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="D180" s="49" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="E180" s="49" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="F180" s="50" t="s">
         <v>51</v>
@@ -13158,7 +13218,7 @@
         <v>38</v>
       </c>
       <c r="I180" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J180" s="51">
         <v>45881</v>
@@ -13188,19 +13248,19 @@
     </row>
     <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="48" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="B181" s="49" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C181" s="49" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="D181" s="49" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="E181" s="49" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="F181" s="50" t="s">
         <v>51</v>
@@ -13212,7 +13272,7 @@
         <v>38</v>
       </c>
       <c r="I181" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J181" s="51">
         <v>45881</v>
@@ -13242,19 +13302,19 @@
     </row>
     <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="48" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B182" s="49" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="C182" s="49" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="D182" s="49" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="E182" s="49" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="F182" s="50" t="s">
         <v>51</v>
@@ -13266,7 +13326,7 @@
         <v>38</v>
       </c>
       <c r="I182" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J182" s="51">
         <v>45881</v>
@@ -13296,19 +13356,19 @@
     </row>
     <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="48" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="B183" s="49" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="C183" s="49" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="D183" s="49" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="E183" s="49" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="F183" s="50" t="s">
         <v>51</v>
@@ -13320,7 +13380,7 @@
         <v>38</v>
       </c>
       <c r="I183" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J183" s="51">
         <v>45881</v>
@@ -13350,19 +13410,19 @@
     </row>
     <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="48" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="B184" s="49" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="C184" s="49" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="D184" s="49" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="E184" s="49" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F184" s="50" t="s">
         <v>51</v>
@@ -13374,7 +13434,7 @@
         <v>38</v>
       </c>
       <c r="I184" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J184" s="51">
         <v>45881</v>
@@ -13404,19 +13464,19 @@
     </row>
     <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="48" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="B185" s="60" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="C185" s="60" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D185" s="60" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="E185" s="60" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F185" s="50" t="s">
         <v>51</v>
@@ -13428,7 +13488,7 @@
         <v>38</v>
       </c>
       <c r="I185" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J185" s="51">
         <v>45881</v>
@@ -13458,19 +13518,19 @@
     </row>
     <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="48" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="B186" s="60" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C186" s="60" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D186" s="60" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="E186" s="60" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F186" s="50" t="s">
         <v>51</v>
@@ -13482,7 +13542,7 @@
         <v>38</v>
       </c>
       <c r="I186" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J186" s="51">
         <v>45881</v>
@@ -13512,19 +13572,19 @@
     </row>
     <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="48" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="B187" s="60" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="C187" s="60" t="s">
+        <v>853</v>
+      </c>
+      <c r="D187" s="60" t="s">
         <v>861</v>
       </c>
-      <c r="D187" s="60" t="s">
-        <v>869</v>
-      </c>
       <c r="E187" s="60" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F187" s="50" t="s">
         <v>51</v>
@@ -13536,7 +13596,7 @@
         <v>38</v>
       </c>
       <c r="I187" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J187" s="51">
         <v>45881</v>
@@ -13566,19 +13626,19 @@
     </row>
     <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="48" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="B188" s="60" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C188" s="60" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D188" s="60" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="E188" s="60" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>51</v>
@@ -13590,7 +13650,7 @@
         <v>38</v>
       </c>
       <c r="I188" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J188" s="51">
         <v>45881</v>
@@ -13620,19 +13680,19 @@
     </row>
     <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="48" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="B189" s="60" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C189" s="60" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D189" s="60" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="E189" s="60" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="F189" s="50" t="s">
         <v>51</v>
@@ -13644,7 +13704,7 @@
         <v>38</v>
       </c>
       <c r="I189" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J189" s="51">
         <v>45881</v>
@@ -13674,19 +13734,19 @@
     </row>
     <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="48" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="B190" s="60" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="C190" s="60" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D190" s="60" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="E190" s="60" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="F190" s="50" t="s">
         <v>51</v>
@@ -13698,7 +13758,7 @@
         <v>38</v>
       </c>
       <c r="I190" s="45" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="J190" s="51">
         <v>45881</v>
@@ -13728,19 +13788,19 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="48" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="B191" s="60" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C191" s="60" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="D191" s="60" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="E191" s="60" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="F191" s="50"/>
       <c r="G191" s="50" t="s">
@@ -13748,22 +13808,22 @@
       </c>
       <c r="H191" s="50"/>
       <c r="I191" s="45" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="J191" s="51"/>
       <c r="K191" s="47"/>
       <c r="L191" s="50"/>
       <c r="N191" s="51"/>
       <c r="O191" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
       <c r="P191" s="53">
-        <v>46192.964436180555</v>
+        <v>46193.00202148149</v>
       </c>
     </row>
     <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="42" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="B192" s="42"/>
       <c r="C192" s="42"/>
@@ -13793,31 +13853,31 @@
     </row>
     <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="48" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="B193" s="49" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="C193" s="49" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="D193" s="49" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="E193" s="49" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="F193" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G193" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H193" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I193" s="45" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="J193" s="51">
         <v>45881</v>
@@ -13832,8 +13892,12 @@
       <c r="N193" s="51">
         <v>45987</v>
       </c>
-      <c r="O193" s="4"/>
-      <c r="P193" s="4"/>
+      <c r="O193" s="4">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P193" s="4">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q193" s="4"/>
       <c r="R193" s="4"/>
       <c r="S193" s="4"/>
@@ -13847,31 +13911,31 @@
     </row>
     <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="48" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="B194" s="49" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="C194" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D194" s="49" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="E194" s="49" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="F194" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G194" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H194" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I194" s="45" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="J194" s="51">
         <v>45881</v>
@@ -13886,8 +13950,12 @@
       <c r="N194" s="51">
         <v>45987</v>
       </c>
-      <c r="O194" s="4"/>
-      <c r="P194" s="4"/>
+      <c r="O194" s="4">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P194" s="4">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q194" s="4"/>
       <c r="R194" s="4"/>
       <c r="S194" s="4"/>
@@ -13901,31 +13969,31 @@
     </row>
     <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="48" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="B195" s="49" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="C195" s="49" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="D195" s="49" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="E195" s="49" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="F195" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G195" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H195" s="50" t="s">
         <v>38</v>
       </c>
       <c r="I195" s="45" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="J195" s="51">
         <v>45881</v>
@@ -13940,8 +14008,12 @@
       <c r="N195" s="51">
         <v>45987</v>
       </c>
-      <c r="O195" s="4"/>
-      <c r="P195" s="4"/>
+      <c r="O195" s="4">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P195" s="4">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q195" s="4"/>
       <c r="R195" s="4"/>
       <c r="S195" s="4"/>
@@ -13955,19 +14027,19 @@
     </row>
     <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="48" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="B196" s="49" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="C196" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D196" s="49" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="E196" s="49" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="F196" s="50" t="s">
         <v>51</v>
@@ -13979,7 +14051,7 @@
         <v>38</v>
       </c>
       <c r="I196" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J196" s="51">
         <v>45881</v>
@@ -14009,19 +14081,19 @@
     </row>
     <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="48" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="B197" s="49" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="E197" s="49" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="F197" s="50" t="s">
         <v>51</v>
@@ -14033,7 +14105,7 @@
         <v>38</v>
       </c>
       <c r="I197" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J197" s="51">
         <v>45881</v>
@@ -14063,19 +14135,19 @@
     </row>
     <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="48" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="B198" s="49" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="C198" s="49" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="E198" s="49" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="F198" s="50" t="s">
         <v>51</v>
@@ -14087,7 +14159,7 @@
         <v>38</v>
       </c>
       <c r="I198" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J198" s="51">
         <v>45881</v>
@@ -14117,19 +14189,19 @@
     </row>
     <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="48" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="B199" s="49" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="E199" s="49" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="F199" s="50" t="s">
         <v>51</v>
@@ -14141,7 +14213,7 @@
         <v>38</v>
       </c>
       <c r="I199" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J199" s="51">
         <v>45881</v>
@@ -14171,19 +14243,19 @@
     </row>
     <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="48" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="B200" s="49" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="C200" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D200" s="49" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="E200" s="49" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="F200" s="50" t="s">
         <v>51</v>
@@ -14195,7 +14267,7 @@
         <v>38</v>
       </c>
       <c r="I200" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J200" s="51">
         <v>45881</v>
@@ -14225,19 +14297,19 @@
     </row>
     <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="48" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="B201" s="49" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="C201" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D201" s="49" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="E201" s="49" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="F201" s="50" t="s">
         <v>51</v>
@@ -14249,7 +14321,7 @@
         <v>38</v>
       </c>
       <c r="I201" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J201" s="51">
         <v>45881</v>
@@ -14279,19 +14351,19 @@
     </row>
     <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="48" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="B202" s="49" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="C202" s="49" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="D202" s="49" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="E202" s="49" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="F202" s="50" t="s">
         <v>51</v>
@@ -14303,7 +14375,7 @@
         <v>38</v>
       </c>
       <c r="I202" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J202" s="51">
         <v>45881</v>
@@ -14333,19 +14405,19 @@
     </row>
     <row r="203" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A203" s="48" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="B203" s="49" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C203" s="49" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="E203" s="49" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="F203" s="50" t="s">
         <v>51</v>
@@ -14357,7 +14429,7 @@
         <v>38</v>
       </c>
       <c r="I203" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J203" s="51">
         <v>45881</v>
@@ -14387,19 +14459,19 @@
     </row>
     <row r="204" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A204" s="48" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="B204" s="49" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="C204" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D204" s="49" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="E204" s="49" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="F204" s="50" t="s">
         <v>51</v>
@@ -14411,7 +14483,7 @@
         <v>38</v>
       </c>
       <c r="I204" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J204" s="51">
         <v>45881</v>
@@ -14441,19 +14513,19 @@
     </row>
     <row r="205" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A205" s="48" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="B205" s="49" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="C205" s="49" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="D205" s="49" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="E205" s="49" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="F205" s="50" t="s">
         <v>51</v>
@@ -14465,7 +14537,7 @@
         <v>38</v>
       </c>
       <c r="I205" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J205" s="51">
         <v>45881</v>
@@ -14495,19 +14567,19 @@
     </row>
     <row r="206" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A206" s="48" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="B206" s="49" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="C206" s="49" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D206" s="49" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="E206" s="49" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="F206" s="50" t="s">
         <v>51</v>
@@ -14519,7 +14591,7 @@
         <v>38</v>
       </c>
       <c r="I206" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J206" s="51">
         <v>45881</v>
@@ -14549,19 +14621,19 @@
     </row>
     <row r="207" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A207" s="48" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="B207" s="49" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="C207" s="49" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="D207" s="49" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="E207" s="49" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="F207" s="50" t="s">
         <v>51</v>
@@ -14573,7 +14645,7 @@
         <v>38</v>
       </c>
       <c r="I207" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J207" s="51">
         <v>45881</v>
@@ -14603,19 +14675,19 @@
     </row>
     <row r="208" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A208" s="48" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="B208" s="49" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="C208" s="49" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="D208" s="49" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="E208" s="49" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="F208" s="50" t="s">
         <v>51</v>
@@ -14627,7 +14699,7 @@
         <v>38</v>
       </c>
       <c r="I208" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J208" s="51">
         <v>45881</v>
@@ -14657,19 +14729,19 @@
     </row>
     <row r="209" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A209" s="48" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="B209" s="49" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="C209" s="49" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D209" s="49" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="E209" s="49" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="F209" s="50" t="s">
         <v>51</v>
@@ -14681,7 +14753,7 @@
         <v>38</v>
       </c>
       <c r="I209" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J209" s="51">
         <v>45881</v>
@@ -14711,19 +14783,19 @@
     </row>
     <row r="210" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A210" s="48" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="B210" s="49" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="C210" s="49" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="D210" s="49" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="E210" s="49" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="F210" s="50" t="s">
         <v>51</v>
@@ -14735,7 +14807,7 @@
         <v>38</v>
       </c>
       <c r="I210" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J210" s="51">
         <v>45881</v>
@@ -14765,19 +14837,19 @@
     </row>
     <row r="211" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A211" s="48" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="B211" s="49" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="C211" s="49" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="D211" s="49" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="E211" s="49" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="F211" s="50" t="s">
         <v>51</v>
@@ -14789,7 +14861,7 @@
         <v>38</v>
       </c>
       <c r="I211" s="45" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="J211" s="51">
         <v>45881</v>
@@ -14819,7 +14891,7 @@
     </row>
     <row r="212" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A212" s="54" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="B212" s="54"/>
       <c r="C212" s="54"/>
@@ -14857,25 +14929,25 @@
     </row>
     <row r="213" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A213" s="48" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="B213" s="49" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="C213" s="49" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="D213" s="49" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="E213" s="49" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="F213" s="50" t="s">
         <v>51</v>
       </c>
       <c r="G213" s="50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H213" s="50" t="s">
         <v>38</v>
@@ -14896,8 +14968,12 @@
       <c r="N213" s="51">
         <v>45987</v>
       </c>
-      <c r="O213" s="4"/>
-      <c r="P213" s="4"/>
+      <c r="O213" s="4">
+        <v>46193.00202148149</v>
+      </c>
+      <c r="P213" s="4">
+        <v>46193.00202148149</v>
+      </c>
       <c r="Q213" s="4"/>
       <c r="R213" s="4"/>
       <c r="S213" s="4"/>
@@ -14911,19 +14987,19 @@
     </row>
     <row r="214" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A214" s="48" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="B214" s="49" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="C214" s="49" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="D214" s="49" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="E214" s="49" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="F214" s="50" t="s">
         <v>51</v>
@@ -14935,7 +15011,7 @@
         <v>38</v>
       </c>
       <c r="I214" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J214" s="51">
         <v>45881</v>
@@ -14965,19 +15041,19 @@
     </row>
     <row r="215" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A215" s="48" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="B215" s="49" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="C215" s="49" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="D215" s="49" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E215" s="49" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="F215" s="50" t="s">
         <v>51</v>
@@ -14989,7 +15065,7 @@
         <v>38</v>
       </c>
       <c r="I215" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J215" s="51">
         <v>45881</v>
@@ -15019,19 +15095,19 @@
     </row>
     <row r="216" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A216" s="48" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="B216" s="49" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="C216" s="49" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="D216" s="49" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="E216" s="49" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="F216" s="50" t="s">
         <v>51</v>
@@ -15043,7 +15119,7 @@
         <v>38</v>
       </c>
       <c r="I216" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J216" s="51">
         <v>45881</v>
@@ -15073,19 +15149,19 @@
     </row>
     <row r="217" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A217" s="48" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="B217" s="49" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="C217" s="49" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="D217" s="49" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="E217" s="49" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="F217" s="50" t="s">
         <v>51</v>
@@ -15097,7 +15173,7 @@
         <v>38</v>
       </c>
       <c r="I217" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J217" s="51">
         <v>45881</v>
@@ -15127,19 +15203,19 @@
     </row>
     <row r="218" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A218" s="48" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="B218" s="49" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="C218" s="49" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="D218" s="49" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E218" s="49" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="F218" s="50" t="s">
         <v>51</v>
@@ -15151,7 +15227,7 @@
         <v>38</v>
       </c>
       <c r="I218" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J218" s="51">
         <v>45881</v>
@@ -15181,19 +15257,19 @@
     </row>
     <row r="219" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A219" s="48" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="B219" s="49" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C219" s="49" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="D219" s="49" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="E219" s="49" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="F219" s="50" t="s">
         <v>51</v>
@@ -15205,7 +15281,7 @@
         <v>38</v>
       </c>
       <c r="I219" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J219" s="51">
         <v>45881</v>
@@ -15235,19 +15311,19 @@
     </row>
     <row r="220" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A220" s="48" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="B220" s="49" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C220" s="49" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="D220" s="49" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="E220" s="49" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="F220" s="50" t="s">
         <v>51</v>
@@ -15259,7 +15335,7 @@
         <v>38</v>
       </c>
       <c r="I220" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J220" s="51">
         <v>45881</v>
@@ -15289,19 +15365,19 @@
     </row>
     <row r="221" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A221" s="48" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="B221" s="49" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="C221" s="49" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="E221" s="49" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="F221" s="50" t="s">
         <v>51</v>
@@ -15313,7 +15389,7 @@
         <v>38</v>
       </c>
       <c r="I221" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J221" s="51">
         <v>45881</v>
@@ -15343,19 +15419,19 @@
     </row>
     <row r="222" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A222" s="48" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="B222" s="49" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C222" s="49" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="E222" s="49" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="F222" s="50" t="s">
         <v>51</v>
@@ -15367,7 +15443,7 @@
         <v>38</v>
       </c>
       <c r="I222" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J222" s="51">
         <v>45881</v>
@@ -15397,19 +15473,19 @@
     </row>
     <row r="223" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A223" s="48" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="B223" s="49" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="C223" s="49" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="D223" s="49" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="E223" s="49" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="F223" s="50" t="s">
         <v>51</v>
@@ -15421,7 +15497,7 @@
         <v>38</v>
       </c>
       <c r="I223" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J223" s="51">
         <v>45881</v>
@@ -15451,19 +15527,19 @@
     </row>
     <row r="224" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A224" s="48" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="B224" s="49" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="C224" s="49" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="D224" s="49" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E224" s="49" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="F224" s="50" t="s">
         <v>51</v>
@@ -15475,7 +15551,7 @@
         <v>38</v>
       </c>
       <c r="I224" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J224" s="51">
         <v>45881</v>
@@ -15505,19 +15581,19 @@
     </row>
     <row r="225" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A225" s="48" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="B225" s="49" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="C225" s="49" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="D225" s="49" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="E225" s="49" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="F225" s="50" t="s">
         <v>51</v>
@@ -15529,7 +15605,7 @@
         <v>38</v>
       </c>
       <c r="I225" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J225" s="51">
         <v>45881</v>
@@ -15559,19 +15635,19 @@
     </row>
     <row r="226" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A226" s="48" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="B226" s="49" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="C226" s="49" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="D226" s="49" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="E226" s="49" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="F226" s="50" t="s">
         <v>51</v>
@@ -15583,7 +15659,7 @@
         <v>38</v>
       </c>
       <c r="I226" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J226" s="51">
         <v>45881</v>
@@ -15613,19 +15689,19 @@
     </row>
     <row r="227" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A227" s="48" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="B227" s="49" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="C227" s="49" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="D227" s="49" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="E227" s="49" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="F227" s="50" t="s">
         <v>51</v>
@@ -15637,7 +15713,7 @@
         <v>38</v>
       </c>
       <c r="I227" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J227" s="51">
         <v>45881</v>
@@ -15667,19 +15743,19 @@
     </row>
     <row r="228" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A228" s="48" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="B228" s="49" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="C228" s="49" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="D228" s="49" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="E228" s="49" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="F228" s="50" t="s">
         <v>51</v>
@@ -15691,7 +15767,7 @@
         <v>38</v>
       </c>
       <c r="I228" s="45" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J228" s="51">
         <v>45881</v>
